--- a/research/traditional_assets/database/data/kenya/kenya_diversified.xlsx
+++ b/research/traditional_assets/database/data/kenya/kenya_diversified.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1502408349175716</v>
+        <v>0.1498216124128189</v>
       </c>
       <c r="C2">
-        <v>17.14010375450532</v>
+        <v>17.05586885202692</v>
       </c>
       <c r="D2">
-        <v>16.74010375450532</v>
+        <v>16.80756885202692</v>
       </c>
       <c r="E2">
-        <v>-13.8</v>
+        <v>-13.6483</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.1517</v>
       </c>
       <c r="G2">
         <v>0.4</v>
@@ -1439,28 +1439,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.007630510000000001</v>
       </c>
       <c r="N2">
-        <v>3.746666666666667</v>
+        <v>3.739036156666667</v>
       </c>
       <c r="O2">
-        <v>1.124</v>
+        <v>1.121710847</v>
       </c>
       <c r="P2">
-        <v>2.622666666666667</v>
+        <v>2.617325309666667</v>
       </c>
       <c r="Q2">
-        <v>3.592666666666667</v>
+        <v>3.587325309666667</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1502408349175716</v>
+        <v>0.1509793054674939</v>
       </c>
       <c r="T2">
-        <v>0.7282077218429368</v>
+        <v>0.7333566653307151</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>491.0113041810661</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1498216124128189</v>
+        <v>0.1494023899080662</v>
       </c>
       <c r="C3">
-        <v>17.05586885202692</v>
+        <v>16.97217993863604</v>
       </c>
       <c r="D3">
-        <v>16.80756885202692</v>
+        <v>16.87557993863604</v>
       </c>
       <c r="E3">
-        <v>-13.6483</v>
+        <v>-13.4966</v>
       </c>
       <c r="F3">
-        <v>0.1517</v>
+        <v>0.3034000000000001</v>
       </c>
       <c r="G3">
         <v>0.4</v>
@@ -1521,28 +1521,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M3">
-        <v>0.007630510000000001</v>
+        <v>0.01526102</v>
       </c>
       <c r="N3">
-        <v>3.739036156666667</v>
+        <v>3.731405646666667</v>
       </c>
       <c r="O3">
-        <v>1.121710847</v>
+        <v>1.119421694</v>
       </c>
       <c r="P3">
-        <v>2.617325309666667</v>
+        <v>2.611983952666667</v>
       </c>
       <c r="Q3">
-        <v>3.587325309666667</v>
+        <v>3.581983952666667</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1509793054674939</v>
+        <v>0.1517328468449655</v>
       </c>
       <c r="T3">
-        <v>0.7333566653307151</v>
+        <v>0.7386106892978359</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>491.0113041810661</v>
+        <v>245.505652090533</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1494023899080662</v>
+        <v>0.1489831674033135</v>
       </c>
       <c r="C4">
-        <v>16.97217993863604</v>
+        <v>16.88904366922377</v>
       </c>
       <c r="D4">
-        <v>16.87557993863604</v>
+        <v>16.94414366922377</v>
       </c>
       <c r="E4">
-        <v>-13.4966</v>
+        <v>-13.3449</v>
       </c>
       <c r="F4">
-        <v>0.3034000000000001</v>
+        <v>0.4551000000000001</v>
       </c>
       <c r="G4">
         <v>0.4</v>
@@ -1603,28 +1603,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M4">
-        <v>0.01526102</v>
+        <v>0.02289153</v>
       </c>
       <c r="N4">
-        <v>3.731405646666667</v>
+        <v>3.723775136666667</v>
       </c>
       <c r="O4">
-        <v>1.119421694</v>
+        <v>1.117132541</v>
       </c>
       <c r="P4">
-        <v>2.611983952666667</v>
+        <v>2.606642595666667</v>
       </c>
       <c r="Q4">
-        <v>3.581983952666667</v>
+        <v>3.576642595666667</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1517328468449655</v>
+        <v>0.1525019251580552</v>
       </c>
       <c r="T4">
-        <v>0.7386106892978359</v>
+        <v>0.7439730436560312</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>245.505652090533</v>
+        <v>163.670434727022</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1489831674033135</v>
+        <v>0.1485639448985608</v>
       </c>
       <c r="C5">
-        <v>16.88904366922377</v>
+        <v>16.80646680727491</v>
       </c>
       <c r="D5">
-        <v>16.94414366922377</v>
+        <v>17.01326680727491</v>
       </c>
       <c r="E5">
-        <v>-13.3449</v>
+        <v>-13.1932</v>
       </c>
       <c r="F5">
-        <v>0.4551000000000001</v>
+        <v>0.6068000000000001</v>
       </c>
       <c r="G5">
         <v>0.4</v>
@@ -1685,28 +1685,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M5">
-        <v>0.02289153</v>
+        <v>0.03052204</v>
       </c>
       <c r="N5">
-        <v>3.723775136666667</v>
+        <v>3.716144626666667</v>
       </c>
       <c r="O5">
-        <v>1.117132541</v>
+        <v>1.114843388</v>
       </c>
       <c r="P5">
-        <v>2.606642595666667</v>
+        <v>2.601301238666667</v>
       </c>
       <c r="Q5">
-        <v>3.576642595666667</v>
+        <v>3.571301238666667</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1525019251580552</v>
+        <v>0.1532870259360008</v>
       </c>
       <c r="T5">
-        <v>0.7439730436560312</v>
+        <v>0.7494471137300224</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>163.670434727022</v>
+        <v>122.7528260452665</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1485639448985608</v>
+        <v>0.148144722393808</v>
       </c>
       <c r="C6">
-        <v>16.80646680727491</v>
+        <v>16.72445622709206</v>
       </c>
       <c r="D6">
-        <v>17.01326680727491</v>
+        <v>17.08295622709206</v>
       </c>
       <c r="E6">
-        <v>-13.1932</v>
+        <v>-13.0415</v>
       </c>
       <c r="F6">
-        <v>0.6068000000000001</v>
+        <v>0.7585000000000002</v>
       </c>
       <c r="G6">
         <v>0.4</v>
@@ -1767,28 +1767,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M6">
-        <v>0.03052204</v>
+        <v>0.03815255000000001</v>
       </c>
       <c r="N6">
-        <v>3.716144626666667</v>
+        <v>3.708514116666667</v>
       </c>
       <c r="O6">
-        <v>1.114843388</v>
+        <v>1.112554235</v>
       </c>
       <c r="P6">
-        <v>2.601301238666667</v>
+        <v>2.595959881666667</v>
       </c>
       <c r="Q6">
-        <v>3.571301238666667</v>
+        <v>3.565959881666667</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1532870259360008</v>
+        <v>0.1540886551513769</v>
       </c>
       <c r="T6">
-        <v>0.7494471137300224</v>
+        <v>0.7550364273845186</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>122.7528260452665</v>
+        <v>98.20226083621321</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.148144722393808</v>
+        <v>0.1477254998890553</v>
       </c>
       <c r="C7">
-        <v>16.72445622709206</v>
+        <v>16.64301891607468</v>
       </c>
       <c r="D7">
-        <v>17.08295622709206</v>
+        <v>17.15321891607468</v>
       </c>
       <c r="E7">
-        <v>-13.0415</v>
+        <v>-12.8898</v>
       </c>
       <c r="F7">
-        <v>0.7585000000000002</v>
+        <v>0.9102000000000001</v>
       </c>
       <c r="G7">
         <v>0.4</v>
@@ -1849,28 +1849,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M7">
-        <v>0.03815255000000001</v>
+        <v>0.04578306</v>
       </c>
       <c r="N7">
-        <v>3.708514116666667</v>
+        <v>3.700883606666667</v>
       </c>
       <c r="O7">
-        <v>1.112554235</v>
+        <v>1.110265082</v>
       </c>
       <c r="P7">
-        <v>2.595959881666667</v>
+        <v>2.590618524666667</v>
       </c>
       <c r="Q7">
-        <v>3.565959881666667</v>
+        <v>3.560618524666666</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1540886551513769</v>
+        <v>0.1549073403075057</v>
       </c>
       <c r="T7">
-        <v>0.7550364273845186</v>
+        <v>0.7607446626061318</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>98.20226083621321</v>
+        <v>81.83521736351102</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1477254998890553</v>
+        <v>0.1473062773843027</v>
       </c>
       <c r="C8">
-        <v>16.64301891607468</v>
+        <v>16.56216197705447</v>
       </c>
       <c r="D8">
-        <v>17.15321891607468</v>
+        <v>17.22406197705447</v>
       </c>
       <c r="E8">
-        <v>-12.8898</v>
+        <v>-12.7381</v>
       </c>
       <c r="F8">
-        <v>0.9102000000000001</v>
+        <v>1.0619</v>
       </c>
       <c r="G8">
         <v>0.4</v>
@@ -1931,28 +1931,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M8">
-        <v>0.04578306</v>
+        <v>0.05341357</v>
       </c>
       <c r="N8">
-        <v>3.700883606666667</v>
+        <v>3.693253096666667</v>
       </c>
       <c r="O8">
-        <v>1.110265082</v>
+        <v>1.107975929</v>
       </c>
       <c r="P8">
-        <v>2.590618524666667</v>
+        <v>2.585277167666667</v>
       </c>
       <c r="Q8">
-        <v>3.560618524666666</v>
+        <v>3.555277167666667</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1549073403075057</v>
+        <v>0.1557436315960244</v>
       </c>
       <c r="T8">
-        <v>0.7607446626061318</v>
+        <v>0.7665756555744464</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>81.83521736351102</v>
+        <v>70.14447202586659</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1473062773843026</v>
+        <v>0.14688705487955</v>
       </c>
       <c r="C9">
-        <v>16.56216197705447</v>
+        <v>16.48189263068901</v>
       </c>
       <c r="D9">
-        <v>17.22406197705448</v>
+        <v>17.29549263068901</v>
       </c>
       <c r="E9">
-        <v>-12.7381</v>
+        <v>-12.5864</v>
       </c>
       <c r="F9">
-        <v>1.0619</v>
+        <v>1.2136</v>
       </c>
       <c r="G9">
         <v>0.4</v>
@@ -2013,28 +2013,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M9">
-        <v>0.05341357000000001</v>
+        <v>0.06104408000000001</v>
       </c>
       <c r="N9">
-        <v>3.693253096666667</v>
+        <v>3.685622586666667</v>
       </c>
       <c r="O9">
-        <v>1.107975929</v>
+        <v>1.105686776</v>
       </c>
       <c r="P9">
-        <v>2.585277167666667</v>
+        <v>2.579935810666667</v>
       </c>
       <c r="Q9">
-        <v>3.555277167666667</v>
+        <v>3.549935810666667</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1557436315960244</v>
+        <v>0.1565981031299456</v>
       </c>
       <c r="T9">
-        <v>0.7665756555744464</v>
+        <v>0.7725334092594635</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>70.14447202586658</v>
+        <v>61.37641302263327</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.14688705487955</v>
+        <v>0.1464678323747972</v>
       </c>
       <c r="C10">
-        <v>16.48189263068901</v>
+        <v>16.40221821791507</v>
       </c>
       <c r="D10">
-        <v>17.29549263068901</v>
+        <v>17.36751821791508</v>
       </c>
       <c r="E10">
-        <v>-12.5864</v>
+        <v>-12.4347</v>
       </c>
       <c r="F10">
-        <v>1.2136</v>
+        <v>1.3653</v>
       </c>
       <c r="G10">
         <v>0.4</v>
@@ -2095,28 +2095,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M10">
-        <v>0.06104408000000001</v>
+        <v>0.06867459000000001</v>
       </c>
       <c r="N10">
-        <v>3.685622586666667</v>
+        <v>3.677992076666667</v>
       </c>
       <c r="O10">
-        <v>1.105686776</v>
+        <v>1.103397623</v>
       </c>
       <c r="P10">
-        <v>2.579935810666667</v>
+        <v>2.574594453666667</v>
       </c>
       <c r="Q10">
-        <v>3.549935810666667</v>
+        <v>3.544594453666667</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1565981031299456</v>
+        <v>0.1574713542580189</v>
       </c>
       <c r="T10">
-        <v>0.7725334092594635</v>
+        <v>0.7786221025859094</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>61.37641302263327</v>
+        <v>54.55681157567401</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1464678323747972</v>
+        <v>0.1460486098700445</v>
       </c>
       <c r="C11">
-        <v>16.40221821791507</v>
+        <v>16.3231462024636</v>
       </c>
       <c r="D11">
-        <v>17.36751821791508</v>
+        <v>17.4401462024636</v>
       </c>
       <c r="E11">
-        <v>-12.4347</v>
+        <v>-12.283</v>
       </c>
       <c r="F11">
-        <v>1.3653</v>
+        <v>1.517</v>
       </c>
       <c r="G11">
         <v>0.4</v>
@@ -2177,28 +2177,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M11">
-        <v>0.06867459000000001</v>
+        <v>0.0763051</v>
       </c>
       <c r="N11">
-        <v>3.677992076666667</v>
+        <v>3.670361566666667</v>
       </c>
       <c r="O11">
-        <v>1.103397623</v>
+        <v>1.10110847</v>
       </c>
       <c r="P11">
-        <v>2.574594453666667</v>
+        <v>2.569253096666667</v>
       </c>
       <c r="Q11">
-        <v>3.544594453666667</v>
+        <v>3.539253096666667</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1574713542580189</v>
+        <v>0.1583640109667161</v>
       </c>
       <c r="T11">
-        <v>0.7786221025859094</v>
+        <v>0.7848461002084985</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>54.55681157567401</v>
+        <v>49.10113041810661</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1460486098700445</v>
+        <v>0.1456293873652918</v>
       </c>
       <c r="C12">
-        <v>16.3231462024636</v>
+        <v>16.24468417343799</v>
       </c>
       <c r="D12">
-        <v>17.4401462024636</v>
+        <v>17.51338417343799</v>
       </c>
       <c r="E12">
-        <v>-12.283</v>
+        <v>-12.1313</v>
       </c>
       <c r="F12">
-        <v>1.517</v>
+        <v>1.6687</v>
       </c>
       <c r="G12">
         <v>0.4</v>
@@ -2259,28 +2259,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M12">
-        <v>0.07630510000000001</v>
+        <v>0.08393561000000001</v>
       </c>
       <c r="N12">
-        <v>3.670361566666667</v>
+        <v>3.662731056666667</v>
       </c>
       <c r="O12">
-        <v>1.10110847</v>
+        <v>1.098819317</v>
       </c>
       <c r="P12">
-        <v>2.569253096666667</v>
+        <v>2.563911739666667</v>
       </c>
       <c r="Q12">
-        <v>3.539253096666667</v>
+        <v>3.533911739666666</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1583640109667161</v>
+        <v>0.1592767273767323</v>
       </c>
       <c r="T12">
-        <v>0.7848461002084985</v>
+        <v>0.7912099629462021</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>49.10113041810661</v>
+        <v>44.63739128918782</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1456293873652918</v>
+        <v>0.1452101648605391</v>
       </c>
       <c r="C13">
-        <v>16.24468417343799</v>
+        <v>16.16683984795764</v>
       </c>
       <c r="D13">
-        <v>17.51338417343799</v>
+        <v>17.58723984795764</v>
       </c>
       <c r="E13">
-        <v>-12.1313</v>
+        <v>-11.9796</v>
       </c>
       <c r="F13">
-        <v>1.6687</v>
+        <v>1.8204</v>
       </c>
       <c r="G13">
         <v>0.4</v>
@@ -2341,28 +2341,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M13">
-        <v>0.08393561000000001</v>
+        <v>0.09156612</v>
       </c>
       <c r="N13">
-        <v>3.662731056666667</v>
+        <v>3.655100546666667</v>
       </c>
       <c r="O13">
-        <v>1.098819317</v>
+        <v>1.096530164</v>
       </c>
       <c r="P13">
-        <v>2.563911739666667</v>
+        <v>2.558570382666667</v>
       </c>
       <c r="Q13">
-        <v>3.533911739666666</v>
+        <v>3.528570382666667</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1592767273767323</v>
+        <v>0.1602101873415217</v>
       </c>
       <c r="T13">
-        <v>0.7912099629462021</v>
+        <v>0.7977184589279445</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>44.63739128918782</v>
+        <v>40.91760868175551</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1452101648605391</v>
+        <v>0.1447909423557864</v>
       </c>
       <c r="C14">
-        <v>16.16683984795764</v>
+        <v>16.08962107386868</v>
       </c>
       <c r="D14">
-        <v>17.58723984795764</v>
+        <v>17.66172107386868</v>
       </c>
       <c r="E14">
-        <v>-11.9796</v>
+        <v>-11.8279</v>
       </c>
       <c r="F14">
-        <v>1.8204</v>
+        <v>1.9721</v>
       </c>
       <c r="G14">
         <v>0.4</v>
@@ -2423,28 +2423,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M14">
-        <v>0.09156612</v>
+        <v>0.09919663000000001</v>
       </c>
       <c r="N14">
-        <v>3.655100546666667</v>
+        <v>3.647470036666667</v>
       </c>
       <c r="O14">
-        <v>1.096530164</v>
+        <v>1.094241011</v>
       </c>
       <c r="P14">
-        <v>2.558570382666667</v>
+        <v>2.553229025666667</v>
       </c>
       <c r="Q14">
-        <v>3.528570382666667</v>
+        <v>3.523229025666667</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1602101873415217</v>
+        <v>0.1611651061560763</v>
       </c>
       <c r="T14">
-        <v>0.7977184589279445</v>
+        <v>0.8043765755069681</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>40.91760868175551</v>
+        <v>37.77010032162048</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1447909423557864</v>
+        <v>0.1443717198510336</v>
       </c>
       <c r="C15">
-        <v>16.08962107386868</v>
+        <v>16.01303583252381</v>
       </c>
       <c r="D15">
-        <v>17.66172107386868</v>
+        <v>17.73683583252381</v>
       </c>
       <c r="E15">
-        <v>-11.8279</v>
+        <v>-11.6762</v>
       </c>
       <c r="F15">
-        <v>1.9721</v>
+        <v>2.123800000000001</v>
       </c>
       <c r="G15">
         <v>0.4</v>
@@ -2505,28 +2505,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M15">
-        <v>0.09919663000000001</v>
+        <v>0.10682714</v>
       </c>
       <c r="N15">
-        <v>3.647470036666667</v>
+        <v>3.639839526666667</v>
       </c>
       <c r="O15">
-        <v>1.094241011</v>
+        <v>1.091951858</v>
       </c>
       <c r="P15">
-        <v>2.553229025666667</v>
+        <v>2.547887668666667</v>
       </c>
       <c r="Q15">
-        <v>3.523229025666667</v>
+        <v>3.517887668666667</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1611651061560763</v>
+        <v>0.1621422323849228</v>
       </c>
       <c r="T15">
-        <v>0.8043765755069681</v>
+        <v>0.8111895320064342</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>37.77010032162048</v>
+        <v>35.07223601293329</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1443717198510336</v>
+        <v>0.1439524973462809</v>
       </c>
       <c r="C16">
-        <v>16.01303583252381</v>
+        <v>15.93709224163345</v>
       </c>
       <c r="D16">
-        <v>17.73683583252381</v>
+        <v>17.81259224163345</v>
       </c>
       <c r="E16">
-        <v>-11.6762</v>
+        <v>-11.5245</v>
       </c>
       <c r="F16">
-        <v>2.123800000000001</v>
+        <v>2.275500000000001</v>
       </c>
       <c r="G16">
         <v>0.4</v>
@@ -2587,28 +2587,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M16">
-        <v>0.10682714</v>
+        <v>0.11445765</v>
       </c>
       <c r="N16">
-        <v>3.639839526666667</v>
+        <v>3.632209016666667</v>
       </c>
       <c r="O16">
-        <v>1.091951858</v>
+        <v>1.089662705</v>
       </c>
       <c r="P16">
-        <v>2.547887668666667</v>
+        <v>2.542546311666667</v>
       </c>
       <c r="Q16">
-        <v>3.517887668666667</v>
+        <v>3.512546311666667</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1621422323849228</v>
+        <v>0.163142349819154</v>
       </c>
       <c r="T16">
-        <v>0.8111895320064342</v>
+        <v>0.8181627933647113</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>35.07223601293329</v>
+        <v>32.7340869454044</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1439524973462809</v>
+        <v>0.1435332748415282</v>
       </c>
       <c r="C17">
-        <v>15.93709224163345</v>
+        <v>15.86179855819027</v>
       </c>
       <c r="D17">
-        <v>17.81259224163345</v>
+        <v>17.88899855819027</v>
       </c>
       <c r="E17">
-        <v>-11.5245</v>
+        <v>-11.3728</v>
       </c>
       <c r="F17">
-        <v>2.2755</v>
+        <v>2.4272</v>
       </c>
       <c r="G17">
         <v>0.4</v>
@@ -2669,28 +2669,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M17">
-        <v>0.11445765</v>
+        <v>0.12208816</v>
       </c>
       <c r="N17">
-        <v>3.632209016666667</v>
+        <v>3.624578506666667</v>
       </c>
       <c r="O17">
-        <v>1.089662705</v>
+        <v>1.087373552</v>
       </c>
       <c r="P17">
-        <v>2.542546311666667</v>
+        <v>2.537204954666667</v>
       </c>
       <c r="Q17">
-        <v>3.512546311666667</v>
+        <v>3.507204954666666</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.163142349819154</v>
+        <v>0.1641662795732479</v>
       </c>
       <c r="T17">
-        <v>0.8181627933647113</v>
+        <v>0.8253020847553284</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>32.73408694540441</v>
+        <v>30.68820651131663</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1435332748415282</v>
+        <v>0.1431140523367755</v>
       </c>
       <c r="C18">
-        <v>15.86179855819027</v>
+        <v>15.78716318146922</v>
       </c>
       <c r="D18">
-        <v>17.88899855819027</v>
+        <v>17.96606318146922</v>
       </c>
       <c r="E18">
-        <v>-11.3728</v>
+        <v>-11.2211</v>
       </c>
       <c r="F18">
-        <v>2.4272</v>
+        <v>2.5789</v>
       </c>
       <c r="G18">
         <v>0.4</v>
@@ -2751,28 +2751,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M18">
-        <v>0.12208816</v>
+        <v>0.12971867</v>
       </c>
       <c r="N18">
-        <v>3.624578506666667</v>
+        <v>3.616947996666667</v>
       </c>
       <c r="O18">
-        <v>1.087373552</v>
+        <v>1.085084399</v>
       </c>
       <c r="P18">
-        <v>2.537204954666667</v>
+        <v>2.531863597666667</v>
       </c>
       <c r="Q18">
-        <v>3.507204954666666</v>
+        <v>3.501863597666667</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1641662795732479</v>
+        <v>0.1652148823334645</v>
       </c>
       <c r="T18">
-        <v>0.8253020847553284</v>
+        <v>0.8326134072637916</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>30.68820651131663</v>
+        <v>28.88301789300389</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1431140523367755</v>
+        <v>0.1426948298320228</v>
       </c>
       <c r="C19">
-        <v>15.78716318146922</v>
+        <v>15.71319465610558</v>
       </c>
       <c r="D19">
-        <v>17.96606318146922</v>
+        <v>18.04379465610558</v>
       </c>
       <c r="E19">
-        <v>-11.2211</v>
+        <v>-11.0694</v>
       </c>
       <c r="F19">
-        <v>2.5789</v>
+        <v>2.730600000000001</v>
       </c>
       <c r="G19">
         <v>0.4</v>
@@ -2833,28 +2833,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M19">
-        <v>0.12971867</v>
+        <v>0.13734918</v>
       </c>
       <c r="N19">
-        <v>3.616947996666667</v>
+        <v>3.609317486666667</v>
       </c>
       <c r="O19">
-        <v>1.085084399</v>
+        <v>1.082795246</v>
       </c>
       <c r="P19">
-        <v>2.531863597666667</v>
+        <v>2.526522240666667</v>
       </c>
       <c r="Q19">
-        <v>3.501863597666667</v>
+        <v>3.496522240666667</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1652148823334645</v>
+        <v>0.1662890607707595</v>
       </c>
       <c r="T19">
-        <v>0.8326134072637916</v>
+        <v>0.8401030547114856</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>28.88301789300389</v>
+        <v>27.278405787837</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1426948298320228</v>
+        <v>0.1422756073272701</v>
       </c>
       <c r="C20">
-        <v>15.71319465610557</v>
+        <v>15.63990167525307</v>
       </c>
       <c r="D20">
-        <v>18.04379465610557</v>
+        <v>18.12220167525308</v>
       </c>
       <c r="E20">
-        <v>-11.0694</v>
+        <v>-10.9177</v>
       </c>
       <c r="F20">
-        <v>2.7306</v>
+        <v>2.8823</v>
       </c>
       <c r="G20">
         <v>0.4</v>
@@ -2915,28 +2915,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M20">
-        <v>0.13734918</v>
+        <v>0.14497969</v>
       </c>
       <c r="N20">
-        <v>3.609317486666667</v>
+        <v>3.601686976666667</v>
       </c>
       <c r="O20">
-        <v>1.082795246</v>
+        <v>1.080506093</v>
       </c>
       <c r="P20">
-        <v>2.526522240666667</v>
+        <v>2.521180883666667</v>
       </c>
       <c r="Q20">
-        <v>3.496522240666667</v>
+        <v>3.491180883666667</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1662890607707595</v>
+        <v>0.1673897621324322</v>
       </c>
       <c r="T20">
-        <v>0.8401030547114856</v>
+        <v>0.8477776317257893</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>27.278405787837</v>
+        <v>25.84270022005611</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1422756073272701</v>
+        <v>0.1418563848225174</v>
       </c>
       <c r="C21">
-        <v>15.63990167525307</v>
+        <v>15.56729308382493</v>
       </c>
       <c r="D21">
-        <v>18.12220167525308</v>
+        <v>18.20129308382494</v>
       </c>
       <c r="E21">
-        <v>-10.9177</v>
+        <v>-10.766</v>
       </c>
       <c r="F21">
-        <v>2.8823</v>
+        <v>3.034000000000001</v>
       </c>
       <c r="G21">
         <v>0.4</v>
@@ -2997,28 +2997,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M21">
-        <v>0.14497969</v>
+        <v>0.1526102</v>
       </c>
       <c r="N21">
-        <v>3.601686976666667</v>
+        <v>3.594056466666667</v>
       </c>
       <c r="O21">
-        <v>1.080506093</v>
+        <v>1.07821694</v>
       </c>
       <c r="P21">
-        <v>2.521180883666667</v>
+        <v>2.515839526666667</v>
       </c>
       <c r="Q21">
-        <v>3.491180883666667</v>
+        <v>3.485839526666667</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1673897621324322</v>
+        <v>0.1685179810281467</v>
       </c>
       <c r="T21">
-        <v>0.8477776317257893</v>
+        <v>0.8556440731654508</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>25.84270022005611</v>
+        <v>24.5505652090533</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1418563848225174</v>
+        <v>0.1414371623177647</v>
       </c>
       <c r="C22">
-        <v>15.56729308382493</v>
+        <v>15.49537788181995</v>
       </c>
       <c r="D22">
-        <v>18.20129308382494</v>
+        <v>18.28107788181995</v>
       </c>
       <c r="E22">
-        <v>-10.766</v>
+        <v>-10.6143</v>
       </c>
       <c r="F22">
-        <v>3.034000000000001</v>
+        <v>3.185700000000001</v>
       </c>
       <c r="G22">
         <v>0.4</v>
@@ -3079,28 +3079,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M22">
-        <v>0.1526102</v>
+        <v>0.16024071</v>
       </c>
       <c r="N22">
-        <v>3.594056466666667</v>
+        <v>3.586425956666667</v>
       </c>
       <c r="O22">
-        <v>1.07821694</v>
+        <v>1.075927787</v>
       </c>
       <c r="P22">
-        <v>2.515839526666667</v>
+        <v>2.510498169666667</v>
       </c>
       <c r="Q22">
-        <v>3.485839526666667</v>
+        <v>3.480498169666666</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1685179810281467</v>
+        <v>0.1696747624275502</v>
       </c>
       <c r="T22">
-        <v>0.8556440731654508</v>
+        <v>0.8637096650213061</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>24.5505652090533</v>
+        <v>23.38149067528886</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1414371623177646</v>
+        <v>0.1410179398130119</v>
       </c>
       <c r="C23">
-        <v>15.49537788181995</v>
+        <v>15.42416522773655</v>
       </c>
       <c r="D23">
-        <v>18.28107788181995</v>
+        <v>18.36156522773655</v>
       </c>
       <c r="E23">
-        <v>-10.6143</v>
+        <v>-10.4626</v>
       </c>
       <c r="F23">
-        <v>3.1857</v>
+        <v>3.337400000000001</v>
       </c>
       <c r="G23">
         <v>0.4</v>
@@ -3161,28 +3161,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M23">
-        <v>0.16024071</v>
+        <v>0.16787122</v>
       </c>
       <c r="N23">
-        <v>3.586425956666667</v>
+        <v>3.578795446666667</v>
       </c>
       <c r="O23">
-        <v>1.075927787</v>
+        <v>1.073638634</v>
       </c>
       <c r="P23">
-        <v>2.510498169666667</v>
+        <v>2.505156812666667</v>
       </c>
       <c r="Q23">
-        <v>3.480498169666666</v>
+        <v>3.475156812666667</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1696747624275502</v>
+        <v>0.1708612048884768</v>
       </c>
       <c r="T23">
-        <v>0.863709665021306</v>
+        <v>0.8719820669247473</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>23.38149067528886</v>
+        <v>22.31869564459392</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1410179398130119</v>
+        <v>0.1405987173082592</v>
       </c>
       <c r="C24">
-        <v>15.42416522773655</v>
+        <v>15.35366444207741</v>
       </c>
       <c r="D24">
-        <v>18.36156522773655</v>
+        <v>18.44276444207742</v>
       </c>
       <c r="E24">
-        <v>-10.4626</v>
+        <v>-10.3109</v>
       </c>
       <c r="F24">
-        <v>3.337400000000001</v>
+        <v>3.489100000000001</v>
       </c>
       <c r="G24">
         <v>0.4</v>
@@ -3243,28 +3243,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M24">
-        <v>0.16787122</v>
+        <v>0.17550173</v>
       </c>
       <c r="N24">
-        <v>3.578795446666667</v>
+        <v>3.571164936666667</v>
       </c>
       <c r="O24">
-        <v>1.073638634</v>
+        <v>1.071349481</v>
       </c>
       <c r="P24">
-        <v>2.505156812666667</v>
+        <v>2.499815455666667</v>
       </c>
       <c r="Q24">
-        <v>3.475156812666667</v>
+        <v>3.469815455666667</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1708612048884768</v>
+        <v>0.1720784640367003</v>
       </c>
       <c r="T24">
-        <v>0.8719820669247473</v>
+        <v>0.8804693364100963</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>22.31869564459392</v>
+        <v>21.34831757308983</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1405987173082592</v>
+        <v>0.1401794948035065</v>
       </c>
       <c r="C25">
-        <v>15.35366444207741</v>
+        <v>15.28388501094747</v>
       </c>
       <c r="D25">
-        <v>18.44276444207742</v>
+        <v>18.52468501094747</v>
       </c>
       <c r="E25">
-        <v>-10.3109</v>
+        <v>-10.1592</v>
       </c>
       <c r="F25">
-        <v>3.489100000000001</v>
+        <v>3.6408</v>
       </c>
       <c r="G25">
         <v>0.4</v>
@@ -3325,28 +3325,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M25">
-        <v>0.17550173</v>
+        <v>0.18313224</v>
       </c>
       <c r="N25">
-        <v>3.571164936666667</v>
+        <v>3.563534426666667</v>
       </c>
       <c r="O25">
-        <v>1.071349481</v>
+        <v>1.069060328</v>
       </c>
       <c r="P25">
-        <v>2.499815455666667</v>
+        <v>2.494474098666667</v>
       </c>
       <c r="Q25">
-        <v>3.469815455666667</v>
+        <v>3.464474098666667</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1720784640367003</v>
+        <v>0.1733277563204033</v>
       </c>
       <c r="T25">
-        <v>0.8804693364100963</v>
+        <v>0.8891799550924281</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>21.34831757308983</v>
+        <v>20.45880434087776</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1401794948035065</v>
+        <v>0.1397602722987538</v>
       </c>
       <c r="C26">
-        <v>15.28388501094747</v>
+        <v>15.21483658974827</v>
       </c>
       <c r="D26">
-        <v>18.52468501094747</v>
+        <v>18.60733658974827</v>
       </c>
       <c r="E26">
-        <v>-10.1592</v>
+        <v>-10.0075</v>
       </c>
       <c r="F26">
-        <v>3.6408</v>
+        <v>3.7925</v>
       </c>
       <c r="G26">
         <v>0.4</v>
@@ -3407,28 +3407,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M26">
-        <v>0.18313224</v>
+        <v>0.19076275</v>
       </c>
       <c r="N26">
-        <v>3.563534426666667</v>
+        <v>3.555903916666667</v>
       </c>
       <c r="O26">
-        <v>1.069060328</v>
+        <v>1.066771175</v>
       </c>
       <c r="P26">
-        <v>2.494474098666667</v>
+        <v>2.489132741666667</v>
       </c>
       <c r="Q26">
-        <v>3.464474098666667</v>
+        <v>3.459132741666667</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1733277563204033</v>
+        <v>0.174610363065005</v>
       </c>
       <c r="T26">
-        <v>0.8891799550924281</v>
+        <v>0.8981228569396221</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>20.45880434087776</v>
+        <v>19.64045216724264</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1397602722987538</v>
+        <v>0.1393410497940011</v>
       </c>
       <c r="C27">
-        <v>15.21483658974827</v>
+        <v>15.14652900697161</v>
       </c>
       <c r="D27">
-        <v>18.60733658974827</v>
+        <v>18.69072900697161</v>
       </c>
       <c r="E27">
-        <v>-10.0075</v>
+        <v>-9.8558</v>
       </c>
       <c r="F27">
-        <v>3.7925</v>
+        <v>3.9442</v>
       </c>
       <c r="G27">
         <v>0.4</v>
@@ -3489,28 +3489,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M27">
-        <v>0.19076275</v>
+        <v>0.19839326</v>
       </c>
       <c r="N27">
-        <v>3.555903916666667</v>
+        <v>3.548273406666667</v>
       </c>
       <c r="O27">
-        <v>1.066771175</v>
+        <v>1.064482022</v>
       </c>
       <c r="P27">
-        <v>2.489132741666667</v>
+        <v>2.483791384666667</v>
       </c>
       <c r="Q27">
-        <v>3.459132741666667</v>
+        <v>3.453791384666667</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.174610363065005</v>
+        <v>0.1759276348567582</v>
       </c>
       <c r="T27">
-        <v>0.8981228569396221</v>
+        <v>0.9073074588367401</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>19.64045216724264</v>
+        <v>18.88505016081023</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1393410497940011</v>
+        <v>0.1389218272892484</v>
       </c>
       <c r="C28">
-        <v>15.14652900697161</v>
+        <v>15.07897226809575</v>
       </c>
       <c r="D28">
-        <v>18.69072900697161</v>
+        <v>18.77487226809576</v>
       </c>
       <c r="E28">
-        <v>-9.8558</v>
+        <v>-9.7041</v>
       </c>
       <c r="F28">
-        <v>3.9442</v>
+        <v>4.0959</v>
       </c>
       <c r="G28">
         <v>0.4</v>
@@ -3571,28 +3571,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M28">
-        <v>0.19839326</v>
+        <v>0.20602377</v>
       </c>
       <c r="N28">
-        <v>3.548273406666667</v>
+        <v>3.540642896666667</v>
       </c>
       <c r="O28">
-        <v>1.064482022</v>
+        <v>1.062192869</v>
       </c>
       <c r="P28">
-        <v>2.483791384666667</v>
+        <v>2.478450027666667</v>
       </c>
       <c r="Q28">
-        <v>3.453791384666667</v>
+        <v>3.448450027666667</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1759276348567582</v>
+        <v>0.1772809962866416</v>
       </c>
       <c r="T28">
-        <v>0.9073074588367401</v>
+        <v>0.9167436936625466</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>18.88505016081023</v>
+        <v>18.18560385855801</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1389218272892484</v>
+        <v>0.1385026047844956</v>
       </c>
       <c r="C29">
-        <v>15.07897226809575</v>
+        <v>15.01217655958725</v>
       </c>
       <c r="D29">
-        <v>18.77487226809576</v>
+        <v>18.85977655958725</v>
       </c>
       <c r="E29">
-        <v>-9.7041</v>
+        <v>-9.552399999999999</v>
       </c>
       <c r="F29">
-        <v>4.0959</v>
+        <v>4.247600000000001</v>
       </c>
       <c r="G29">
         <v>0.4</v>
@@ -3653,28 +3653,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M29">
-        <v>0.20602377</v>
+        <v>0.2136542800000001</v>
       </c>
       <c r="N29">
-        <v>3.540642896666667</v>
+        <v>3.533012386666667</v>
       </c>
       <c r="O29">
-        <v>1.062192869</v>
+        <v>1.059903716</v>
       </c>
       <c r="P29">
-        <v>2.478450027666667</v>
+        <v>2.473108670666667</v>
       </c>
       <c r="Q29">
-        <v>3.448450027666667</v>
+        <v>3.443108670666667</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1772809962866416</v>
+        <v>0.1786719510895773</v>
       </c>
       <c r="T29">
-        <v>0.9167436936625466</v>
+        <v>0.9264420461224029</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>18.18560385855801</v>
+        <v>17.53611800646664</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1385026047844956</v>
+        <v>0.1380833822797429</v>
       </c>
       <c r="C30">
-        <v>15.01217655958725</v>
+        <v>14.94615225301188</v>
       </c>
       <c r="D30">
-        <v>18.85977655958725</v>
+        <v>18.94545225301188</v>
       </c>
       <c r="E30">
-        <v>-9.552399999999999</v>
+        <v>-9.400700000000001</v>
       </c>
       <c r="F30">
-        <v>4.247600000000001</v>
+        <v>4.399300000000001</v>
       </c>
       <c r="G30">
         <v>0.4</v>
@@ -3735,28 +3735,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M30">
-        <v>0.2136542800000001</v>
+        <v>0.22128479</v>
       </c>
       <c r="N30">
-        <v>3.533012386666667</v>
+        <v>3.525381876666667</v>
       </c>
       <c r="O30">
-        <v>1.059903716</v>
+        <v>1.057614563</v>
       </c>
       <c r="P30">
-        <v>2.473108670666667</v>
+        <v>2.467767313666667</v>
       </c>
       <c r="Q30">
-        <v>3.443108670666667</v>
+        <v>3.437767313666667</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1786719510895773</v>
+        <v>0.1801020877179478</v>
       </c>
       <c r="T30">
-        <v>0.9264420461224029</v>
+        <v>0.9364135916092976</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>17.53611800646664</v>
+        <v>16.93142428210573</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1380833822797429</v>
+        <v>0.1376641597749902</v>
       </c>
       <c r="C31">
-        <v>14.94615225301188</v>
+        <v>14.88090990925817</v>
       </c>
       <c r="D31">
-        <v>18.94545225301188</v>
+        <v>19.03190990925817</v>
       </c>
       <c r="E31">
-        <v>-9.400700000000001</v>
+        <v>-9.249000000000001</v>
       </c>
       <c r="F31">
-        <v>4.3993</v>
+        <v>4.551</v>
       </c>
       <c r="G31">
         <v>0.4</v>
@@ -3817,28 +3817,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M31">
-        <v>0.22128479</v>
+        <v>0.2289153</v>
       </c>
       <c r="N31">
-        <v>3.525381876666667</v>
+        <v>3.517751366666667</v>
       </c>
       <c r="O31">
-        <v>1.057614563</v>
+        <v>1.05532541</v>
       </c>
       <c r="P31">
-        <v>2.467767313666667</v>
+        <v>2.462425956666667</v>
       </c>
       <c r="Q31">
-        <v>3.437767313666667</v>
+        <v>3.432425956666667</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1801020877179478</v>
+        <v>0.1815730853928432</v>
       </c>
       <c r="T31">
-        <v>0.9364135916092976</v>
+        <v>0.9466700383958179</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>16.93142428210573</v>
+        <v>16.36704347270221</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1376641597749902</v>
+        <v>0.1372449372702375</v>
       </c>
       <c r="C32">
-        <v>14.88090990925817</v>
+        <v>14.8164602828771</v>
       </c>
       <c r="D32">
-        <v>19.03190990925817</v>
+        <v>19.1191602828771</v>
       </c>
       <c r="E32">
-        <v>-9.249000000000001</v>
+        <v>-9.097300000000001</v>
       </c>
       <c r="F32">
-        <v>4.551</v>
+        <v>4.7027</v>
       </c>
       <c r="G32">
         <v>0.4</v>
@@ -3899,28 +3899,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M32">
-        <v>0.2289153</v>
+        <v>0.23654581</v>
       </c>
       <c r="N32">
-        <v>3.517751366666667</v>
+        <v>3.510120856666667</v>
       </c>
       <c r="O32">
-        <v>1.05532541</v>
+        <v>1.053036257</v>
       </c>
       <c r="P32">
-        <v>2.462425956666667</v>
+        <v>2.457084599666667</v>
       </c>
       <c r="Q32">
-        <v>3.432425956666667</v>
+        <v>3.427084599666667</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1815730853928432</v>
+        <v>0.1830867206815036</v>
       </c>
       <c r="T32">
-        <v>0.9466700383958179</v>
+        <v>0.9572237734949908</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>16.36704347270221</v>
+        <v>15.83907432842149</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1372449372702375</v>
+        <v>0.1368257147654848</v>
       </c>
       <c r="C33">
-        <v>14.8164602828771</v>
+        <v>14.75281432654164</v>
       </c>
       <c r="D33">
-        <v>19.1191602828771</v>
+        <v>19.20721432654164</v>
       </c>
       <c r="E33">
-        <v>-9.097300000000001</v>
+        <v>-8.945599999999999</v>
       </c>
       <c r="F33">
-        <v>4.7027</v>
+        <v>4.854400000000001</v>
       </c>
       <c r="G33">
         <v>0.4</v>
@@ -3981,28 +3981,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M33">
-        <v>0.23654581</v>
+        <v>0.24417632</v>
       </c>
       <c r="N33">
-        <v>3.510120856666667</v>
+        <v>3.502490346666667</v>
       </c>
       <c r="O33">
-        <v>1.053036257</v>
+        <v>1.050747104</v>
       </c>
       <c r="P33">
-        <v>2.457084599666667</v>
+        <v>2.451743242666667</v>
       </c>
       <c r="Q33">
-        <v>3.427084599666667</v>
+        <v>3.421743242666667</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1830867206815036</v>
+        <v>0.1846448746551247</v>
       </c>
       <c r="T33">
-        <v>0.9572237734949908</v>
+        <v>0.9680879125676689</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>15.83907432842149</v>
+        <v>15.34410325565831</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1368257147654848</v>
+        <v>0.1364064922607321</v>
       </c>
       <c r="C34">
-        <v>14.75281432654164</v>
+        <v>14.68998319563022</v>
       </c>
       <c r="D34">
-        <v>19.20721432654164</v>
+        <v>19.29608319563022</v>
       </c>
       <c r="E34">
-        <v>-8.945599999999999</v>
+        <v>-8.793900000000001</v>
       </c>
       <c r="F34">
-        <v>4.854400000000001</v>
+        <v>5.006100000000001</v>
       </c>
       <c r="G34">
         <v>0.4</v>
@@ -4063,28 +4063,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M34">
-        <v>0.24417632</v>
+        <v>0.25180683</v>
       </c>
       <c r="N34">
-        <v>3.502490346666667</v>
+        <v>3.494859836666667</v>
       </c>
       <c r="O34">
-        <v>1.050747104</v>
+        <v>1.048457951</v>
       </c>
       <c r="P34">
-        <v>2.451743242666667</v>
+        <v>2.446401885666667</v>
       </c>
       <c r="Q34">
-        <v>3.421743242666667</v>
+        <v>3.416401885666667</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1846448746551247</v>
+        <v>0.1862495406876598</v>
       </c>
       <c r="T34">
-        <v>0.9680879125676689</v>
+        <v>0.9792763542992331</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>15.34410325565831</v>
+        <v>14.87913042972927</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1364064922607321</v>
+        <v>0.1359872697559793</v>
       </c>
       <c r="C35">
-        <v>14.68998319563022</v>
+        <v>14.62797825293794</v>
       </c>
       <c r="D35">
-        <v>19.29608319563022</v>
+        <v>19.38577825293794</v>
       </c>
       <c r="E35">
-        <v>-8.793900000000001</v>
+        <v>-8.642199999999999</v>
       </c>
       <c r="F35">
-        <v>5.006100000000001</v>
+        <v>5.157800000000001</v>
       </c>
       <c r="G35">
         <v>0.4</v>
@@ -4145,28 +4145,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M35">
-        <v>0.25180683</v>
+        <v>0.25943734</v>
       </c>
       <c r="N35">
-        <v>3.494859836666667</v>
+        <v>3.487229326666667</v>
       </c>
       <c r="O35">
-        <v>1.048457951</v>
+        <v>1.046168798</v>
       </c>
       <c r="P35">
-        <v>2.446401885666667</v>
+        <v>2.441060528666667</v>
       </c>
       <c r="Q35">
-        <v>3.416401885666667</v>
+        <v>3.411060528666667</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1862495406876598</v>
+        <v>0.1879028329636051</v>
       </c>
       <c r="T35">
-        <v>0.9792763542992331</v>
+        <v>0.9908038397196322</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>14.87913042972927</v>
+        <v>14.44150894650195</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1359872697559793</v>
+        <v>0.1355680472512266</v>
       </c>
       <c r="C36">
-        <v>14.62797825293794</v>
+        <v>14.56681107351978</v>
       </c>
       <c r="D36">
-        <v>19.38577825293794</v>
+        <v>19.47631107351978</v>
       </c>
       <c r="E36">
-        <v>-8.642199999999999</v>
+        <v>-8.490500000000001</v>
       </c>
       <c r="F36">
-        <v>5.157800000000001</v>
+        <v>5.309500000000001</v>
       </c>
       <c r="G36">
         <v>0.4</v>
@@ -4227,28 +4227,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M36">
-        <v>0.25943734</v>
+        <v>0.2670678500000001</v>
       </c>
       <c r="N36">
-        <v>3.487229326666667</v>
+        <v>3.479598816666667</v>
       </c>
       <c r="O36">
-        <v>1.046168798</v>
+        <v>1.043879645</v>
       </c>
       <c r="P36">
-        <v>2.441060528666667</v>
+        <v>2.435719171666667</v>
       </c>
       <c r="Q36">
-        <v>3.411060528666667</v>
+        <v>3.405719171666667</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1879028329636051</v>
+        <v>0.1896069957711179</v>
       </c>
       <c r="T36">
-        <v>0.9908038397196322</v>
+        <v>1.002686016999121</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>14.44150894650195</v>
+        <v>14.02889440517332</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1355680472512266</v>
+        <v>0.1351488247464739</v>
       </c>
       <c r="C37">
-        <v>14.56681107351978</v>
+        <v>14.50649344967024</v>
       </c>
       <c r="D37">
-        <v>19.47631107351978</v>
+        <v>19.56769344967024</v>
       </c>
       <c r="E37">
-        <v>-8.490500000000001</v>
+        <v>-8.338799999999999</v>
       </c>
       <c r="F37">
-        <v>5.309500000000001</v>
+        <v>5.461200000000002</v>
       </c>
       <c r="G37">
         <v>0.4</v>
@@ -4309,28 +4309,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M37">
-        <v>0.2670678500000001</v>
+        <v>0.2746983600000001</v>
       </c>
       <c r="N37">
-        <v>3.479598816666667</v>
+        <v>3.471968306666667</v>
       </c>
       <c r="O37">
-        <v>1.043879645</v>
+        <v>1.041590492</v>
       </c>
       <c r="P37">
-        <v>2.435719171666667</v>
+        <v>2.430377814666667</v>
       </c>
       <c r="Q37">
-        <v>3.405719171666667</v>
+        <v>3.400377814666667</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1896069957711179</v>
+        <v>0.1913644136663655</v>
       </c>
       <c r="T37">
-        <v>1.002686016999121</v>
+        <v>1.014939512318593</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>14.02889440517332</v>
+        <v>13.6392028939185</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1351488247464739</v>
+        <v>0.1347296022417212</v>
       </c>
       <c r="C38">
-        <v>14.50649344967023</v>
+        <v>14.44703739604376</v>
       </c>
       <c r="D38">
-        <v>19.56769344967023</v>
+        <v>19.65993739604376</v>
       </c>
       <c r="E38">
-        <v>-8.338799999999999</v>
+        <v>-8.187100000000001</v>
       </c>
       <c r="F38">
-        <v>5.461200000000001</v>
+        <v>5.612900000000001</v>
       </c>
       <c r="G38">
         <v>0.4</v>
@@ -4391,28 +4391,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M38">
-        <v>0.27469836</v>
+        <v>0.28232887</v>
       </c>
       <c r="N38">
-        <v>3.471968306666667</v>
+        <v>3.464337796666667</v>
       </c>
       <c r="O38">
-        <v>1.041590492</v>
+        <v>1.039301339</v>
       </c>
       <c r="P38">
-        <v>2.430377814666667</v>
+        <v>2.425036457666667</v>
       </c>
       <c r="Q38">
-        <v>3.400377814666667</v>
+        <v>3.395036457666667</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1913644136663655</v>
+        <v>0.1931776226059067</v>
       </c>
       <c r="T38">
-        <v>1.014939512318593</v>
+        <v>1.027582007489477</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>13.6392028939185</v>
+        <v>13.27057578867746</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1347296022417212</v>
+        <v>0.1343103797369685</v>
       </c>
       <c r="C39">
-        <v>14.44703739604376</v>
+        <v>14.38845515492067</v>
       </c>
       <c r="D39">
-        <v>19.65993739604376</v>
+        <v>19.75305515492067</v>
       </c>
       <c r="E39">
-        <v>-8.187100000000001</v>
+        <v>-8.035399999999999</v>
       </c>
       <c r="F39">
-        <v>5.612900000000001</v>
+        <v>5.764600000000001</v>
       </c>
       <c r="G39">
         <v>0.4</v>
@@ -4473,28 +4473,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M39">
-        <v>0.28232887</v>
+        <v>0.28995938</v>
       </c>
       <c r="N39">
-        <v>3.464337796666667</v>
+        <v>3.456707286666667</v>
       </c>
       <c r="O39">
-        <v>1.039301339</v>
+        <v>1.037012186</v>
       </c>
       <c r="P39">
-        <v>2.425036457666667</v>
+        <v>2.419695100666667</v>
       </c>
       <c r="Q39">
-        <v>3.395036457666667</v>
+        <v>3.389695100666667</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1931776226059067</v>
+        <v>0.1950493221564008</v>
       </c>
       <c r="T39">
-        <v>1.027582007489477</v>
+        <v>1.040632325085229</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>13.27057578867746</v>
+        <v>12.92135011002806</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1343103797369685</v>
+        <v>0.1343006572322158</v>
       </c>
       <c r="C40">
-        <v>14.38845515492067</v>
+        <v>14.23892518595356</v>
       </c>
       <c r="D40">
-        <v>19.75305515492067</v>
+        <v>19.75522518595356</v>
       </c>
       <c r="E40">
-        <v>-8.035399999999999</v>
+        <v>-7.8837</v>
       </c>
       <c r="F40">
-        <v>5.764600000000001</v>
+        <v>5.916300000000001</v>
       </c>
       <c r="G40">
         <v>0.4</v>
@@ -4555,45 +4555,45 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M40">
-        <v>0.28995938</v>
+        <v>0.30646434</v>
       </c>
       <c r="N40">
-        <v>3.456707286666667</v>
+        <v>3.440202326666667</v>
       </c>
       <c r="O40">
-        <v>1.037012186</v>
+        <v>1.032060698</v>
       </c>
       <c r="P40">
-        <v>2.419695100666667</v>
+        <v>2.408141628666667</v>
       </c>
       <c r="Q40">
-        <v>3.389695100666667</v>
+        <v>3.378141628666667</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1950493221564008</v>
+        <v>0.1969823889052718</v>
       </c>
       <c r="T40">
-        <v>1.040632325085229</v>
+        <v>1.054110521946415</v>
       </c>
       <c r="U40">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V40">
         <v>0.3</v>
       </c>
       <c r="W40">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y40">
-        <v>12.92135011002806</v>
+        <v>12.22545718260946</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1343006572322158</v>
+        <v>0.1338919347274631</v>
       </c>
       <c r="C41">
-        <v>14.23892518595356</v>
+        <v>14.17888403241819</v>
       </c>
       <c r="D41">
-        <v>19.75522518595356</v>
+        <v>19.84688403241819</v>
       </c>
       <c r="E41">
-        <v>-7.8837</v>
+        <v>-7.731999999999999</v>
       </c>
       <c r="F41">
-        <v>5.916300000000001</v>
+        <v>6.068000000000001</v>
       </c>
       <c r="G41">
         <v>0.4</v>
@@ -4637,28 +4637,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M41">
-        <v>0.30646434</v>
+        <v>0.3143224000000001</v>
       </c>
       <c r="N41">
-        <v>3.440202326666667</v>
+        <v>3.432344266666667</v>
       </c>
       <c r="O41">
-        <v>1.032060698</v>
+        <v>1.02970328</v>
       </c>
       <c r="P41">
-        <v>2.408141628666667</v>
+        <v>2.402640986666667</v>
       </c>
       <c r="Q41">
-        <v>3.378141628666667</v>
+        <v>3.372640986666667</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1969823889052718</v>
+        <v>0.1989798912124384</v>
       </c>
       <c r="T41">
-        <v>1.054110521946415</v>
+        <v>1.068037992036307</v>
       </c>
       <c r="U41">
         <v>0.0518</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>12.22545718260946</v>
+        <v>11.91982075304422</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1338919347274631</v>
+        <v>0.1334832122227103</v>
       </c>
       <c r="C42">
-        <v>14.17888403241819</v>
+        <v>14.11969738757063</v>
       </c>
       <c r="D42">
-        <v>19.84688403241819</v>
+        <v>19.93939738757063</v>
       </c>
       <c r="E42">
-        <v>-7.731999999999999</v>
+        <v>-7.580299999999999</v>
       </c>
       <c r="F42">
-        <v>6.068000000000001</v>
+        <v>6.219700000000001</v>
       </c>
       <c r="G42">
         <v>0.4</v>
@@ -4719,28 +4719,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M42">
-        <v>0.3143224000000001</v>
+        <v>0.3221804600000001</v>
       </c>
       <c r="N42">
-        <v>3.432344266666667</v>
+        <v>3.424486206666667</v>
       </c>
       <c r="O42">
-        <v>1.02970328</v>
+        <v>1.027345862</v>
       </c>
       <c r="P42">
-        <v>2.402640986666667</v>
+        <v>2.397140344666667</v>
       </c>
       <c r="Q42">
-        <v>3.372640986666667</v>
+        <v>3.367140344666667</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1989798912124384</v>
+        <v>0.2010451054622209</v>
       </c>
       <c r="T42">
-        <v>1.068037992036307</v>
+        <v>1.082437579756365</v>
       </c>
       <c r="U42">
         <v>0.0518</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>11.91982075304422</v>
+        <v>11.62909341760412</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1334832122227103</v>
+        <v>0.1330744897179576</v>
       </c>
       <c r="C43">
-        <v>14.11969738757063</v>
+        <v>14.06137725687545</v>
       </c>
       <c r="D43">
-        <v>19.93939738757063</v>
+        <v>20.03277725687545</v>
       </c>
       <c r="E43">
-        <v>-7.580299999999999</v>
+        <v>-7.428599999999999</v>
       </c>
       <c r="F43">
-        <v>6.219700000000001</v>
+        <v>6.371400000000001</v>
       </c>
       <c r="G43">
         <v>0.4</v>
@@ -4801,28 +4801,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M43">
-        <v>0.3221804600000001</v>
+        <v>0.3300385200000001</v>
       </c>
       <c r="N43">
-        <v>3.424486206666667</v>
+        <v>3.416628146666667</v>
       </c>
       <c r="O43">
-        <v>1.027345862</v>
+        <v>1.024988444</v>
       </c>
       <c r="P43">
-        <v>2.397140344666667</v>
+        <v>2.391639702666667</v>
       </c>
       <c r="Q43">
-        <v>3.367140344666667</v>
+        <v>3.361639702666666</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2010451054622209</v>
+        <v>0.2031815339964787</v>
       </c>
       <c r="T43">
-        <v>1.082437579756365</v>
+        <v>1.097333704984012</v>
       </c>
       <c r="U43">
         <v>0.0518</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>11.62909341760412</v>
+        <v>11.35221024099449</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1330744897179576</v>
+        <v>0.1326657672132049</v>
       </c>
       <c r="C44">
-        <v>14.06137725687545</v>
+        <v>14.00393587175059</v>
       </c>
       <c r="D44">
-        <v>20.03277725687545</v>
+        <v>20.12703587175059</v>
       </c>
       <c r="E44">
-        <v>-7.4286</v>
+        <v>-7.2769</v>
       </c>
       <c r="F44">
-        <v>6.3714</v>
+        <v>6.5231</v>
       </c>
       <c r="G44">
         <v>0.4</v>
@@ -4883,28 +4883,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M44">
-        <v>0.33003852</v>
+        <v>0.33789658</v>
       </c>
       <c r="N44">
-        <v>3.416628146666667</v>
+        <v>3.408770086666667</v>
       </c>
       <c r="O44">
-        <v>1.024988444</v>
+        <v>1.022631026</v>
       </c>
       <c r="P44">
-        <v>2.391639702666667</v>
+        <v>2.386139060666667</v>
       </c>
       <c r="Q44">
-        <v>3.361639702666666</v>
+        <v>3.356139060666667</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2031815339964786</v>
+        <v>0.2053929249354472</v>
       </c>
       <c r="T44">
-        <v>1.097333704984012</v>
+        <v>1.112752501272277</v>
       </c>
       <c r="U44">
         <v>0.0518</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>11.3522102409945</v>
+        <v>11.08820535166904</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1326657672132049</v>
+        <v>0.1322570447084522</v>
       </c>
       <c r="C45">
-        <v>14.00393587175059</v>
+        <v>13.94738569490833</v>
       </c>
       <c r="D45">
-        <v>20.12703587175059</v>
+        <v>20.22218569490833</v>
       </c>
       <c r="E45">
-        <v>-7.2769</v>
+        <v>-7.1252</v>
       </c>
       <c r="F45">
-        <v>6.5231</v>
+        <v>6.674800000000001</v>
       </c>
       <c r="G45">
         <v>0.4</v>
@@ -4965,28 +4965,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M45">
-        <v>0.33789658</v>
+        <v>0.3457546400000001</v>
       </c>
       <c r="N45">
-        <v>3.408770086666667</v>
+        <v>3.400912026666667</v>
       </c>
       <c r="O45">
-        <v>1.022631026</v>
+        <v>1.020273608</v>
       </c>
       <c r="P45">
-        <v>2.386139060666667</v>
+        <v>2.380638418666667</v>
       </c>
       <c r="Q45">
-        <v>3.356139060666667</v>
+        <v>3.350638418666667</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2053929249354472</v>
+        <v>0.2076832941222361</v>
       </c>
       <c r="T45">
-        <v>1.112752501272277</v>
+        <v>1.128721968856552</v>
       </c>
       <c r="U45">
         <v>0.0518</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>11.08820535166904</v>
+        <v>10.83620068458565</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1322570447084522</v>
+        <v>0.1318483222036995</v>
       </c>
       <c r="C46">
-        <v>13.94738569490833</v>
+        <v>13.89173942584837</v>
       </c>
       <c r="D46">
-        <v>20.22218569490833</v>
+        <v>20.31823942584838</v>
       </c>
       <c r="E46">
-        <v>-7.1252</v>
+        <v>-6.9735</v>
       </c>
       <c r="F46">
-        <v>6.674800000000001</v>
+        <v>6.826500000000001</v>
       </c>
       <c r="G46">
         <v>0.4</v>
@@ -5047,28 +5047,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M46">
-        <v>0.3457546400000001</v>
+        <v>0.3536127000000001</v>
       </c>
       <c r="N46">
-        <v>3.400912026666667</v>
+        <v>3.393053966666667</v>
       </c>
       <c r="O46">
-        <v>1.020273608</v>
+        <v>1.01791619</v>
       </c>
       <c r="P46">
-        <v>2.380638418666667</v>
+        <v>2.375137776666667</v>
       </c>
       <c r="Q46">
-        <v>3.350638418666667</v>
+        <v>3.345137776666666</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2076832941222361</v>
+        <v>0.2100569494612718</v>
       </c>
       <c r="T46">
-        <v>1.128721968856552</v>
+        <v>1.145272144352983</v>
       </c>
       <c r="U46">
         <v>0.0518</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>10.83620068458565</v>
+        <v>10.59539622492819</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1318483222036995</v>
+        <v>0.1314395996989468</v>
       </c>
       <c r="C47">
-        <v>13.89173942584837</v>
+        <v>13.8370100065084</v>
       </c>
       <c r="D47">
-        <v>20.31823942584838</v>
+        <v>20.41521000650841</v>
       </c>
       <c r="E47">
-        <v>-6.9735</v>
+        <v>-6.8218</v>
       </c>
       <c r="F47">
-        <v>6.826500000000001</v>
+        <v>6.978200000000001</v>
       </c>
       <c r="G47">
         <v>0.4</v>
@@ -5129,28 +5129,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M47">
-        <v>0.3536127000000001</v>
+        <v>0.3614707600000001</v>
       </c>
       <c r="N47">
-        <v>3.393053966666667</v>
+        <v>3.385195906666667</v>
       </c>
       <c r="O47">
-        <v>1.01791619</v>
+        <v>1.015558772</v>
       </c>
       <c r="P47">
-        <v>2.375137776666667</v>
+        <v>2.369637134666667</v>
       </c>
       <c r="Q47">
-        <v>3.345137776666666</v>
+        <v>3.339637134666667</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2100569494612718</v>
+        <v>0.2125185179610125</v>
       </c>
       <c r="T47">
-        <v>1.145272144352983</v>
+        <v>1.162435289312243</v>
       </c>
       <c r="U47">
         <v>0.0518</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>10.59539622492819</v>
+        <v>10.36506152438628</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1314395996989468</v>
+        <v>0.131030877194194</v>
       </c>
       <c r="C48">
-        <v>13.8370100065084</v>
+        <v>13.78321062707695</v>
       </c>
       <c r="D48">
-        <v>20.41521000650841</v>
+        <v>20.51311062707695</v>
       </c>
       <c r="E48">
-        <v>-6.8218</v>
+        <v>-6.6701</v>
       </c>
       <c r="F48">
-        <v>6.978200000000001</v>
+        <v>7.129900000000001</v>
       </c>
       <c r="G48">
         <v>0.4</v>
@@ -5211,28 +5211,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M48">
-        <v>0.3614707600000001</v>
+        <v>0.3693288200000001</v>
       </c>
       <c r="N48">
-        <v>3.385195906666667</v>
+        <v>3.377337846666667</v>
       </c>
       <c r="O48">
-        <v>1.015558772</v>
+        <v>1.013201354</v>
       </c>
       <c r="P48">
-        <v>2.369637134666667</v>
+        <v>2.364136492666667</v>
       </c>
       <c r="Q48">
-        <v>3.339637134666667</v>
+        <v>3.334136492666667</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2125185179610125</v>
+        <v>0.215072975838102</v>
       </c>
       <c r="T48">
-        <v>1.162435289312243</v>
+        <v>1.180246100119024</v>
       </c>
       <c r="U48">
         <v>0.0518</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>10.36506152438628</v>
+        <v>10.14452830046316</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.131030877194194</v>
+        <v>0.1306221546894413</v>
       </c>
       <c r="C49">
-        <v>13.78321062707695</v>
+        <v>13.7303547319746</v>
       </c>
       <c r="D49">
-        <v>20.51311062707695</v>
+        <v>20.6119547319746</v>
       </c>
       <c r="E49">
-        <v>-6.6701</v>
+        <v>-6.5184</v>
       </c>
       <c r="F49">
-        <v>7.129900000000001</v>
+        <v>7.281600000000001</v>
       </c>
       <c r="G49">
         <v>0.4</v>
@@ -5293,28 +5293,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M49">
-        <v>0.3693288200000001</v>
+        <v>0.3771868800000001</v>
       </c>
       <c r="N49">
-        <v>3.377337846666667</v>
+        <v>3.369479786666667</v>
       </c>
       <c r="O49">
-        <v>1.013201354</v>
+        <v>1.010843936</v>
       </c>
       <c r="P49">
-        <v>2.364136492666667</v>
+        <v>2.358635850666667</v>
       </c>
       <c r="Q49">
-        <v>3.334136492666667</v>
+        <v>3.328635850666667</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.215072975838102</v>
+        <v>0.2177256820950795</v>
       </c>
       <c r="T49">
-        <v>1.180246100119024</v>
+        <v>1.198741942110681</v>
       </c>
       <c r="U49">
         <v>0.0518</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>10.14452830046316</v>
+        <v>9.933183960870183</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1306221546894413</v>
+        <v>0.1307965321846886</v>
       </c>
       <c r="C50">
-        <v>13.7303547319746</v>
+        <v>13.53636758277065</v>
       </c>
       <c r="D50">
-        <v>20.6119547319746</v>
+        <v>20.56966758277065</v>
       </c>
       <c r="E50">
-        <v>-6.5184</v>
+        <v>-6.3667</v>
       </c>
       <c r="F50">
-        <v>7.281600000000001</v>
+        <v>7.433300000000001</v>
       </c>
       <c r="G50">
         <v>0.4</v>
@@ -5375,45 +5375,45 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M50">
-        <v>0.3771868800000001</v>
+        <v>0.3976815500000001</v>
       </c>
       <c r="N50">
-        <v>3.369479786666667</v>
+        <v>3.348985116666667</v>
       </c>
       <c r="O50">
-        <v>1.010843936</v>
+        <v>1.004695535</v>
       </c>
       <c r="P50">
-        <v>2.358635850666667</v>
+        <v>2.344289581666667</v>
       </c>
       <c r="Q50">
-        <v>3.328635850666667</v>
+        <v>3.314289581666666</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2177256820950795</v>
+        <v>0.2204824160484091</v>
       </c>
       <c r="T50">
-        <v>1.198741942110681</v>
+        <v>1.217963111239265</v>
       </c>
       <c r="U50">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V50">
         <v>0.3</v>
       </c>
       <c r="W50">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y50">
-        <v>9.933183960870183</v>
+        <v>9.4212735457973</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1307965321846886</v>
+        <v>0.1303997096799359</v>
       </c>
       <c r="C51">
-        <v>13.53636758277065</v>
+        <v>13.48115144829462</v>
       </c>
       <c r="D51">
-        <v>20.56966758277065</v>
+        <v>20.66615144829462</v>
       </c>
       <c r="E51">
-        <v>-6.3667</v>
+        <v>-6.215</v>
       </c>
       <c r="F51">
-        <v>7.433300000000001</v>
+        <v>7.585000000000001</v>
       </c>
       <c r="G51">
         <v>0.4</v>
@@ -5457,28 +5457,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M51">
-        <v>0.3976815500000001</v>
+        <v>0.4057975</v>
       </c>
       <c r="N51">
-        <v>3.348985116666667</v>
+        <v>3.340869166666667</v>
       </c>
       <c r="O51">
-        <v>1.004695535</v>
+        <v>1.00226075</v>
       </c>
       <c r="P51">
-        <v>2.344289581666667</v>
+        <v>2.338608416666667</v>
       </c>
       <c r="Q51">
-        <v>3.314289581666666</v>
+        <v>3.308608416666667</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2204824160484091</v>
+        <v>0.2233494193598718</v>
       </c>
       <c r="T51">
-        <v>1.217963111239265</v>
+        <v>1.237953127132992</v>
       </c>
       <c r="U51">
         <v>0.0535</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>9.4212735457973</v>
+        <v>9.232848074881355</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1303997096799359</v>
+        <v>0.1300028871751832</v>
       </c>
       <c r="C52">
-        <v>13.48115144829462</v>
+        <v>13.4268447118326</v>
       </c>
       <c r="D52">
-        <v>20.66615144829462</v>
+        <v>20.7635447118326</v>
       </c>
       <c r="E52">
-        <v>-6.215</v>
+        <v>-6.0633</v>
       </c>
       <c r="F52">
-        <v>7.585000000000001</v>
+        <v>7.736700000000001</v>
       </c>
       <c r="G52">
         <v>0.4</v>
@@ -5539,28 +5539,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M52">
-        <v>0.4057975</v>
+        <v>0.41391345</v>
       </c>
       <c r="N52">
-        <v>3.340869166666667</v>
+        <v>3.332753216666667</v>
       </c>
       <c r="O52">
-        <v>1.00226075</v>
+        <v>0.9998259650000001</v>
       </c>
       <c r="P52">
-        <v>2.338608416666667</v>
+        <v>2.332927251666667</v>
       </c>
       <c r="Q52">
-        <v>3.308608416666667</v>
+        <v>3.302927251666667</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2233494193598718</v>
+        <v>0.2263334432146596</v>
       </c>
       <c r="T52">
-        <v>1.237953127132992</v>
+        <v>1.258759062042791</v>
       </c>
       <c r="U52">
         <v>0.0535</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>9.232848074881355</v>
+        <v>9.051811838118976</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1300028871751832</v>
+        <v>0.1296060646704305</v>
       </c>
       <c r="C53">
-        <v>13.4268447118326</v>
+        <v>13.37346029140905</v>
       </c>
       <c r="D53">
-        <v>20.7635447118326</v>
+        <v>20.86186029140905</v>
       </c>
       <c r="E53">
-        <v>-6.0633</v>
+        <v>-5.9116</v>
       </c>
       <c r="F53">
-        <v>7.736700000000001</v>
+        <v>7.888400000000001</v>
       </c>
       <c r="G53">
         <v>0.4</v>
@@ -5621,28 +5621,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M53">
-        <v>0.41391345</v>
+        <v>0.4220294000000001</v>
       </c>
       <c r="N53">
-        <v>3.332753216666667</v>
+        <v>3.324637266666667</v>
       </c>
       <c r="O53">
-        <v>0.9998259650000001</v>
+        <v>0.99739118</v>
       </c>
       <c r="P53">
-        <v>2.332927251666667</v>
+        <v>2.327246086666667</v>
       </c>
       <c r="Q53">
-        <v>3.302927251666667</v>
+        <v>3.297246086666667</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2263334432146596</v>
+        <v>0.2294418013967301</v>
       </c>
       <c r="T53">
-        <v>1.258759062042791</v>
+        <v>1.280431910907164</v>
       </c>
       <c r="U53">
         <v>0.0535</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>9.051811838118976</v>
+        <v>8.877738533539764</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1296060646704305</v>
+        <v>0.1292092421656778</v>
       </c>
       <c r="C54">
-        <v>13.37346029140905</v>
+        <v>13.3210113508803</v>
       </c>
       <c r="D54">
-        <v>20.86186029140905</v>
+        <v>20.9611113508803</v>
       </c>
       <c r="E54">
-        <v>-5.9116</v>
+        <v>-5.7599</v>
       </c>
       <c r="F54">
-        <v>7.888400000000001</v>
+        <v>8.040100000000001</v>
       </c>
       <c r="G54">
         <v>0.4</v>
@@ -5703,28 +5703,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M54">
-        <v>0.4220294000000001</v>
+        <v>0.43014535</v>
       </c>
       <c r="N54">
-        <v>3.324637266666667</v>
+        <v>3.316521316666667</v>
       </c>
       <c r="O54">
-        <v>0.99739118</v>
+        <v>0.994956395</v>
       </c>
       <c r="P54">
-        <v>2.327246086666667</v>
+        <v>2.321564921666667</v>
       </c>
       <c r="Q54">
-        <v>3.297246086666667</v>
+        <v>3.291564921666667</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2294418013967301</v>
+        <v>0.2326824301397399</v>
       </c>
       <c r="T54">
-        <v>1.280431910907164</v>
+        <v>1.303027008659383</v>
       </c>
       <c r="U54">
         <v>0.0535</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>8.877738533539764</v>
+        <v>8.710234032906939</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1292092421656778</v>
+        <v>0.128812419660925</v>
       </c>
       <c r="C55">
-        <v>13.3210113508803</v>
+        <v>13.26951130581032</v>
       </c>
       <c r="D55">
-        <v>20.9611113508803</v>
+        <v>21.06131130581032</v>
       </c>
       <c r="E55">
-        <v>-5.7599</v>
+        <v>-5.6082</v>
       </c>
       <c r="F55">
-        <v>8.040100000000001</v>
+        <v>8.191800000000001</v>
       </c>
       <c r="G55">
         <v>0.4</v>
@@ -5785,28 +5785,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M55">
-        <v>0.43014535</v>
+        <v>0.4382613</v>
       </c>
       <c r="N55">
-        <v>3.316521316666667</v>
+        <v>3.308405366666667</v>
       </c>
       <c r="O55">
-        <v>0.994956395</v>
+        <v>0.9925216100000001</v>
       </c>
       <c r="P55">
-        <v>2.321564921666667</v>
+        <v>2.315883756666667</v>
       </c>
       <c r="Q55">
-        <v>3.291564921666667</v>
+        <v>3.285883756666666</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2326824301397399</v>
+        <v>0.2360639557846197</v>
       </c>
       <c r="T55">
-        <v>1.303027008659383</v>
+        <v>1.326604501966046</v>
       </c>
       <c r="U55">
         <v>0.0535</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>8.710234032906939</v>
+        <v>8.54893340266792</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.128812419660925</v>
+        <v>0.1284155971561723</v>
       </c>
       <c r="C56">
-        <v>13.26951130581032</v>
+        <v>13.21897382951574</v>
       </c>
       <c r="D56">
-        <v>21.06131130581032</v>
+        <v>21.16247382951574</v>
       </c>
       <c r="E56">
-        <v>-5.6082</v>
+        <v>-5.456499999999998</v>
       </c>
       <c r="F56">
-        <v>8.191800000000001</v>
+        <v>8.343500000000002</v>
       </c>
       <c r="G56">
         <v>0.4</v>
@@ -5867,28 +5867,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M56">
-        <v>0.4382613</v>
+        <v>0.4463772500000001</v>
       </c>
       <c r="N56">
-        <v>3.308405366666667</v>
+        <v>3.300289416666667</v>
       </c>
       <c r="O56">
-        <v>0.9925216100000001</v>
+        <v>0.990086825</v>
       </c>
       <c r="P56">
-        <v>2.315883756666667</v>
+        <v>2.310202591666667</v>
       </c>
       <c r="Q56">
-        <v>3.285883756666666</v>
+        <v>3.280202591666667</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2360639557846197</v>
+        <v>0.2395957714581607</v>
       </c>
       <c r="T56">
-        <v>1.326604501966046</v>
+        <v>1.351229883864116</v>
       </c>
       <c r="U56">
         <v>0.0535</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>8.54893340266792</v>
+        <v>8.39349824989214</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1284155971561723</v>
+        <v>0.1280187746514196</v>
       </c>
       <c r="C57">
-        <v>13.21897382951574</v>
+        <v>13.16941285928595</v>
       </c>
       <c r="D57">
-        <v>21.16247382951574</v>
+        <v>21.26461285928596</v>
       </c>
       <c r="E57">
-        <v>-5.456499999999998</v>
+        <v>-5.304799999999998</v>
       </c>
       <c r="F57">
-        <v>8.343500000000002</v>
+        <v>8.495200000000002</v>
       </c>
       <c r="G57">
         <v>0.4</v>
@@ -5949,28 +5949,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M57">
-        <v>0.4463772500000001</v>
+        <v>0.4544932000000001</v>
       </c>
       <c r="N57">
-        <v>3.300289416666667</v>
+        <v>3.292173466666667</v>
       </c>
       <c r="O57">
-        <v>0.990086825</v>
+        <v>0.9876520400000001</v>
       </c>
       <c r="P57">
-        <v>2.310202591666667</v>
+        <v>2.304521426666667</v>
       </c>
       <c r="Q57">
-        <v>3.280202591666667</v>
+        <v>3.274521426666667</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2395957714581607</v>
+        <v>0.2432881242077719</v>
       </c>
       <c r="T57">
-        <v>1.351229883864116</v>
+        <v>1.376974601303008</v>
       </c>
       <c r="U57">
         <v>0.0535</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>8.39349824989214</v>
+        <v>8.243614352572639</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1280187746514196</v>
+        <v>0.1276219521466669</v>
       </c>
       <c r="C58">
-        <v>13.16941285928595</v>
+        <v>13.12084260278429</v>
       </c>
       <c r="D58">
-        <v>21.26461285928596</v>
+        <v>21.36774260278429</v>
       </c>
       <c r="E58">
-        <v>-5.304799999999998</v>
+        <v>-5.153099999999998</v>
       </c>
       <c r="F58">
-        <v>8.495200000000002</v>
+        <v>8.646900000000002</v>
       </c>
       <c r="G58">
         <v>0.4</v>
@@ -6031,28 +6031,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M58">
-        <v>0.4544932000000001</v>
+        <v>0.4626091500000001</v>
       </c>
       <c r="N58">
-        <v>3.292173466666667</v>
+        <v>3.284057516666667</v>
       </c>
       <c r="O58">
-        <v>0.9876520400000001</v>
+        <v>0.985217255</v>
       </c>
       <c r="P58">
-        <v>2.304521426666667</v>
+        <v>2.298840261666667</v>
       </c>
       <c r="Q58">
-        <v>3.274521426666667</v>
+        <v>3.268840261666667</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2432881242077719</v>
+        <v>0.2471522142945742</v>
       </c>
       <c r="T58">
-        <v>1.376974601303008</v>
+        <v>1.403916747459987</v>
       </c>
       <c r="U58">
         <v>0.0535</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>8.243614352572639</v>
+        <v>8.098989539369608</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1276219521466669</v>
+        <v>0.1272251296419142</v>
       </c>
       <c r="C59">
-        <v>13.12084260278429</v>
+        <v>13.07327754463624</v>
       </c>
       <c r="D59">
-        <v>21.36774260278429</v>
+        <v>21.47187754463624</v>
       </c>
       <c r="E59">
-        <v>-5.153099999999998</v>
+        <v>-5.001399999999999</v>
       </c>
       <c r="F59">
-        <v>8.646900000000002</v>
+        <v>8.798600000000002</v>
       </c>
       <c r="G59">
         <v>0.4</v>
@@ -6113,28 +6113,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M59">
-        <v>0.4626091500000001</v>
+        <v>0.4707251000000001</v>
       </c>
       <c r="N59">
-        <v>3.284057516666667</v>
+        <v>3.275941566666667</v>
       </c>
       <c r="O59">
-        <v>0.985217255</v>
+        <v>0.9827824700000001</v>
       </c>
       <c r="P59">
-        <v>2.298840261666667</v>
+        <v>2.293159096666667</v>
       </c>
       <c r="Q59">
-        <v>3.268840261666667</v>
+        <v>3.263159096666667</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2471522142945742</v>
+        <v>0.2512003086712243</v>
       </c>
       <c r="T59">
-        <v>1.403916747459987</v>
+        <v>1.432141852957776</v>
       </c>
       <c r="U59">
         <v>0.0535</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>8.098989539369608</v>
+        <v>7.959351788690822</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1272251296419142</v>
+        <v>0.1268283071371615</v>
       </c>
       <c r="C60">
-        <v>13.07327754463624</v>
+        <v>13.02673245321138</v>
       </c>
       <c r="D60">
-        <v>21.47187754463624</v>
+        <v>21.57703245321138</v>
       </c>
       <c r="E60">
-        <v>-5.0014</v>
+        <v>-4.8497</v>
       </c>
       <c r="F60">
-        <v>8.7986</v>
+        <v>8.9503</v>
       </c>
       <c r="G60">
         <v>0.4</v>
@@ -6195,28 +6195,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M60">
-        <v>0.4707251</v>
+        <v>0.47884105</v>
       </c>
       <c r="N60">
-        <v>3.275941566666667</v>
+        <v>3.267825616666667</v>
       </c>
       <c r="O60">
-        <v>0.9827824700000001</v>
+        <v>0.9803476850000001</v>
       </c>
       <c r="P60">
-        <v>2.293159096666667</v>
+        <v>2.287477931666667</v>
       </c>
       <c r="Q60">
-        <v>3.263159096666667</v>
+        <v>3.257477931666667</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2512003086712242</v>
+        <v>0.2554458710662474</v>
       </c>
       <c r="T60">
-        <v>1.432141852957775</v>
+        <v>1.46174379287009</v>
       </c>
       <c r="U60">
         <v>0.0535</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>7.959351788690824</v>
+        <v>7.824447521085895</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1268283071371615</v>
+        <v>0.1264314846324087</v>
       </c>
       <c r="C61">
-        <v>13.02673245321138</v>
+        <v>12.98122238760547</v>
       </c>
       <c r="D61">
-        <v>21.57703245321138</v>
+        <v>21.68322238760547</v>
       </c>
       <c r="E61">
-        <v>-4.8497</v>
+        <v>-4.698</v>
       </c>
       <c r="F61">
-        <v>8.9503</v>
+        <v>9.102</v>
       </c>
       <c r="G61">
         <v>0.4</v>
@@ -6277,28 +6277,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M61">
-        <v>0.47884105</v>
+        <v>0.486957</v>
       </c>
       <c r="N61">
-        <v>3.267825616666667</v>
+        <v>3.259709666666667</v>
       </c>
       <c r="O61">
-        <v>0.9803476850000001</v>
+        <v>0.9779129000000001</v>
       </c>
       <c r="P61">
-        <v>2.287477931666667</v>
+        <v>2.281796766666667</v>
       </c>
       <c r="Q61">
-        <v>3.257477931666667</v>
+        <v>3.251796766666667</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2554458710662474</v>
+        <v>0.2599037115810219</v>
       </c>
       <c r="T61">
-        <v>1.46174379287009</v>
+        <v>1.49282582977802</v>
       </c>
       <c r="U61">
         <v>0.0535</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>7.824447521085895</v>
+        <v>7.69404006240113</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1264314846324087</v>
+        <v>0.126376262127656</v>
       </c>
       <c r="C62">
-        <v>12.98122238760547</v>
+        <v>12.84438286660681</v>
       </c>
       <c r="D62">
-        <v>21.68322238760547</v>
+        <v>21.69808286660681</v>
       </c>
       <c r="E62">
-        <v>-4.698</v>
+        <v>-4.5463</v>
       </c>
       <c r="F62">
-        <v>9.102</v>
+        <v>9.2537</v>
       </c>
       <c r="G62">
         <v>0.4</v>
@@ -6359,45 +6359,45 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M62">
-        <v>0.486957</v>
+        <v>0.50247591</v>
       </c>
       <c r="N62">
-        <v>3.259709666666667</v>
+        <v>3.244190756666667</v>
       </c>
       <c r="O62">
-        <v>0.9779129000000001</v>
+        <v>0.9732572269999999</v>
       </c>
       <c r="P62">
-        <v>2.281796766666667</v>
+        <v>2.270933529666667</v>
       </c>
       <c r="Q62">
-        <v>3.251796766666667</v>
+        <v>3.240933529666667</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2599037115810219</v>
+        <v>0.2645901593016821</v>
       </c>
       <c r="T62">
-        <v>1.49282582977802</v>
+        <v>1.525501817296613</v>
       </c>
       <c r="U62">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V62">
         <v>0.3</v>
       </c>
       <c r="W62">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y62">
-        <v>7.69404006240113</v>
+        <v>7.456410530539995</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.126376262127656</v>
+        <v>0.1259850396229033</v>
       </c>
       <c r="C63">
-        <v>12.84438286660681</v>
+        <v>12.79854773076759</v>
       </c>
       <c r="D63">
-        <v>21.69808286660681</v>
+        <v>21.80394773076759</v>
       </c>
       <c r="E63">
-        <v>-4.5463</v>
+        <v>-4.394600000000001</v>
       </c>
       <c r="F63">
-        <v>9.2537</v>
+        <v>9.4054</v>
       </c>
       <c r="G63">
         <v>0.4</v>
@@ -6441,28 +6441,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M63">
-        <v>0.50247591</v>
+        <v>0.51071322</v>
       </c>
       <c r="N63">
-        <v>3.244190756666667</v>
+        <v>3.235953446666667</v>
       </c>
       <c r="O63">
-        <v>0.9732572269999999</v>
+        <v>0.9707860340000001</v>
       </c>
       <c r="P63">
-        <v>2.270933529666667</v>
+        <v>2.265167412666667</v>
       </c>
       <c r="Q63">
-        <v>3.240933529666667</v>
+        <v>3.235167412666667</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2645901593016821</v>
+        <v>0.269523262165535</v>
       </c>
       <c r="T63">
-        <v>1.525501817296613</v>
+        <v>1.559897593631975</v>
       </c>
       <c r="U63">
         <v>0.0543</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>7.456410530539995</v>
+        <v>7.336145844563545</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1259850396229033</v>
+        <v>0.1255938171181506</v>
       </c>
       <c r="C64">
-        <v>12.79854773076759</v>
+        <v>12.75375068832503</v>
       </c>
       <c r="D64">
-        <v>21.80394773076759</v>
+        <v>21.91085068832503</v>
       </c>
       <c r="E64">
-        <v>-4.394600000000001</v>
+        <v>-4.242899999999999</v>
       </c>
       <c r="F64">
-        <v>9.4054</v>
+        <v>9.557100000000002</v>
       </c>
       <c r="G64">
         <v>0.4</v>
@@ -6523,28 +6523,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M64">
-        <v>0.51071322</v>
+        <v>0.5189505300000001</v>
       </c>
       <c r="N64">
-        <v>3.235953446666667</v>
+        <v>3.227716136666667</v>
       </c>
       <c r="O64">
-        <v>0.9707860340000001</v>
+        <v>0.968314841</v>
       </c>
       <c r="P64">
-        <v>2.265167412666667</v>
+        <v>2.259401295666667</v>
       </c>
       <c r="Q64">
-        <v>3.235167412666667</v>
+        <v>3.229401295666666</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.269523262165535</v>
+        <v>0.2747230192382449</v>
       </c>
       <c r="T64">
-        <v>1.559897593631975</v>
+        <v>1.596152601120599</v>
       </c>
       <c r="U64">
         <v>0.0543</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>7.336145844563545</v>
+        <v>7.219699085126026</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1255938171181506</v>
+        <v>0.1252025946133979</v>
       </c>
       <c r="C65">
-        <v>12.75375068832503</v>
+        <v>12.71000708356986</v>
       </c>
       <c r="D65">
-        <v>21.91085068832503</v>
+        <v>22.01880708356986</v>
       </c>
       <c r="E65">
-        <v>-4.242899999999999</v>
+        <v>-4.091199999999999</v>
       </c>
       <c r="F65">
-        <v>9.557100000000002</v>
+        <v>9.708800000000002</v>
       </c>
       <c r="G65">
         <v>0.4</v>
@@ -6605,28 +6605,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M65">
-        <v>0.5189505300000001</v>
+        <v>0.5271878400000001</v>
       </c>
       <c r="N65">
-        <v>3.227716136666667</v>
+        <v>3.219478826666667</v>
       </c>
       <c r="O65">
-        <v>0.968314841</v>
+        <v>0.9658436480000001</v>
       </c>
       <c r="P65">
-        <v>2.259401295666667</v>
+        <v>2.253635178666667</v>
       </c>
       <c r="Q65">
-        <v>3.229401295666666</v>
+        <v>3.223635178666667</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2747230192382449</v>
+        <v>0.280211651703883</v>
       </c>
       <c r="T65">
-        <v>1.596152601120599</v>
+        <v>1.634421775691925</v>
       </c>
       <c r="U65">
         <v>0.0543</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>7.219699085126026</v>
+        <v>7.106891286920932</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1252025946133979</v>
+        <v>0.1248113721086452</v>
       </c>
       <c r="C66">
-        <v>12.71000708356986</v>
+        <v>12.66733256470004</v>
       </c>
       <c r="D66">
-        <v>22.01880708356986</v>
+        <v>22.12783256470005</v>
       </c>
       <c r="E66">
-        <v>-4.091199999999999</v>
+        <v>-3.939499999999999</v>
       </c>
       <c r="F66">
-        <v>9.708800000000002</v>
+        <v>9.860500000000002</v>
       </c>
       <c r="G66">
         <v>0.4</v>
@@ -6687,28 +6687,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M66">
-        <v>0.5271878400000001</v>
+        <v>0.5354251500000001</v>
       </c>
       <c r="N66">
-        <v>3.219478826666667</v>
+        <v>3.211241516666667</v>
       </c>
       <c r="O66">
-        <v>0.9658436480000001</v>
+        <v>0.963372455</v>
       </c>
       <c r="P66">
-        <v>2.253635178666667</v>
+        <v>2.247869061666667</v>
       </c>
       <c r="Q66">
-        <v>3.223635178666667</v>
+        <v>3.217869061666667</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.280211651703883</v>
+        <v>0.2860139203104148</v>
       </c>
       <c r="T66">
-        <v>1.634421775691925</v>
+        <v>1.674877760238755</v>
       </c>
       <c r="U66">
         <v>0.0543</v>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>7.106891286920932</v>
+        <v>6.997554497891379</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1248113721086452</v>
+        <v>0.1244201496038925</v>
       </c>
       <c r="C67">
-        <v>12.66733256470004</v>
+        <v>12.62574309138215</v>
       </c>
       <c r="D67">
-        <v>22.12783256470005</v>
+        <v>22.23794309138215</v>
       </c>
       <c r="E67">
-        <v>-3.939499999999999</v>
+        <v>-3.787799999999999</v>
       </c>
       <c r="F67">
-        <v>9.860500000000002</v>
+        <v>10.0122</v>
       </c>
       <c r="G67">
         <v>0.4</v>
@@ -6769,28 +6769,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M67">
-        <v>0.5354251500000001</v>
+        <v>0.5436624600000001</v>
       </c>
       <c r="N67">
-        <v>3.211241516666667</v>
+        <v>3.203004206666667</v>
       </c>
       <c r="O67">
-        <v>0.963372455</v>
+        <v>0.960901262</v>
       </c>
       <c r="P67">
-        <v>2.247869061666667</v>
+        <v>2.242102944666667</v>
       </c>
       <c r="Q67">
-        <v>3.217869061666667</v>
+        <v>3.212102944666666</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2860139203104148</v>
+        <v>0.2921574988349778</v>
       </c>
       <c r="T67">
-        <v>1.674877760238755</v>
+        <v>1.717713508582457</v>
       </c>
       <c r="U67">
         <v>0.0543</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>6.997554497891379</v>
+        <v>6.891530944893025</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1244201496038925</v>
+        <v>0.1240289270991397</v>
       </c>
       <c r="C68">
-        <v>12.62574309138215</v>
+        <v>12.58525494253963</v>
       </c>
       <c r="D68">
-        <v>22.23794309138215</v>
+        <v>22.34915494253963</v>
       </c>
       <c r="E68">
-        <v>-3.787799999999999</v>
+        <v>-3.636099999999999</v>
       </c>
       <c r="F68">
-        <v>10.0122</v>
+        <v>10.1639</v>
       </c>
       <c r="G68">
         <v>0.4</v>
@@ -6851,28 +6851,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M68">
-        <v>0.5436624600000001</v>
+        <v>0.5518997700000001</v>
       </c>
       <c r="N68">
-        <v>3.203004206666667</v>
+        <v>3.194766896666667</v>
       </c>
       <c r="O68">
-        <v>0.960901262</v>
+        <v>0.9584300689999999</v>
       </c>
       <c r="P68">
-        <v>2.242102944666667</v>
+        <v>2.236336827666667</v>
       </c>
       <c r="Q68">
-        <v>3.212102944666666</v>
+        <v>3.206336827666667</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2921574988349778</v>
+        <v>0.2986734154519387</v>
       </c>
       <c r="T68">
-        <v>1.717713508582457</v>
+        <v>1.763145362886384</v>
       </c>
       <c r="U68">
         <v>0.0543</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>6.891530944893025</v>
+        <v>6.788672274073726</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1240289270991397</v>
+        <v>0.123637704594387</v>
       </c>
       <c r="C69">
-        <v>12.58525494253963</v>
+        <v>12.54588472437594</v>
       </c>
       <c r="D69">
-        <v>22.34915494253963</v>
+        <v>22.46148472437595</v>
       </c>
       <c r="E69">
-        <v>-3.636099999999999</v>
+        <v>-3.484399999999999</v>
       </c>
       <c r="F69">
-        <v>10.1639</v>
+        <v>10.3156</v>
       </c>
       <c r="G69">
         <v>0.4</v>
@@ -6933,28 +6933,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M69">
-        <v>0.5518997700000001</v>
+        <v>0.5601370800000001</v>
       </c>
       <c r="N69">
-        <v>3.194766896666667</v>
+        <v>3.186529586666667</v>
       </c>
       <c r="O69">
-        <v>0.9584300689999999</v>
+        <v>0.9559588760000001</v>
       </c>
       <c r="P69">
-        <v>2.236336827666667</v>
+        <v>2.230570710666667</v>
       </c>
       <c r="Q69">
-        <v>3.206336827666667</v>
+        <v>3.200570710666667</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2986734154519387</v>
+        <v>0.3055965768574596</v>
       </c>
       <c r="T69">
-        <v>1.763145362886384</v>
+        <v>1.811416708084306</v>
       </c>
       <c r="U69">
         <v>0.0543</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>6.788672274073726</v>
+        <v>6.688838858278524</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.123637704594387</v>
+        <v>0.1232464820896343</v>
       </c>
       <c r="C70">
-        <v>12.54588472437594</v>
+        <v>12.50764937864087</v>
       </c>
       <c r="D70">
-        <v>22.46148472437595</v>
+        <v>22.57494937864088</v>
       </c>
       <c r="E70">
-        <v>-3.484399999999999</v>
+        <v>-3.332699999999999</v>
       </c>
       <c r="F70">
-        <v>10.3156</v>
+        <v>10.4673</v>
       </c>
       <c r="G70">
         <v>0.4</v>
@@ -7015,28 +7015,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M70">
-        <v>0.5601370800000001</v>
+        <v>0.5683743900000001</v>
       </c>
       <c r="N70">
-        <v>3.186529586666667</v>
+        <v>3.178292276666667</v>
       </c>
       <c r="O70">
-        <v>0.9559588760000001</v>
+        <v>0.953487683</v>
       </c>
       <c r="P70">
-        <v>2.230570710666667</v>
+        <v>2.224804593666667</v>
       </c>
       <c r="Q70">
-        <v>3.200570710666667</v>
+        <v>3.194804593666666</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3055965768574596</v>
+        <v>0.3129663938375301</v>
       </c>
       <c r="T70">
-        <v>1.811416708084306</v>
+        <v>1.862802333617577</v>
       </c>
       <c r="U70">
         <v>0.0543</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>6.688838858278524</v>
+        <v>6.591899164680284</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1232464820896343</v>
+        <v>0.1228552595848816</v>
       </c>
       <c r="C71">
-        <v>12.50764937864087</v>
+        <v>12.47056619114864</v>
       </c>
       <c r="D71">
-        <v>22.57494937864088</v>
+        <v>22.68956619114865</v>
       </c>
       <c r="E71">
-        <v>-3.332699999999999</v>
+        <v>-3.180999999999999</v>
       </c>
       <c r="F71">
-        <v>10.4673</v>
+        <v>10.619</v>
       </c>
       <c r="G71">
         <v>0.4</v>
@@ -7097,28 +7097,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M71">
-        <v>0.5683743900000001</v>
+        <v>0.5766117000000001</v>
       </c>
       <c r="N71">
-        <v>3.178292276666667</v>
+        <v>3.170054966666667</v>
       </c>
       <c r="O71">
-        <v>0.953487683</v>
+        <v>0.9510164900000001</v>
       </c>
       <c r="P71">
-        <v>2.224804593666667</v>
+        <v>2.219038476666667</v>
       </c>
       <c r="Q71">
-        <v>3.194804593666666</v>
+        <v>3.189038476666667</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3129663938375301</v>
+        <v>0.3208275319496054</v>
       </c>
       <c r="T71">
-        <v>1.862802333617577</v>
+        <v>1.917613667519734</v>
       </c>
       <c r="U71">
         <v>0.0543</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>6.591899164680284</v>
+        <v>6.497729176613424</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1228552595848816</v>
+        <v>0.1224640370801289</v>
       </c>
       <c r="C72">
-        <v>12.47056619114864</v>
+        <v>12.43465280055685</v>
       </c>
       <c r="D72">
-        <v>22.68956619114865</v>
+        <v>22.80535280055685</v>
       </c>
       <c r="E72">
-        <v>-3.180999999999999</v>
+        <v>-3.029299999999999</v>
       </c>
       <c r="F72">
-        <v>10.619</v>
+        <v>10.7707</v>
       </c>
       <c r="G72">
         <v>0.4</v>
@@ -7179,28 +7179,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M72">
-        <v>0.5766117000000001</v>
+        <v>0.5848490100000001</v>
       </c>
       <c r="N72">
-        <v>3.170054966666667</v>
+        <v>3.161817656666667</v>
       </c>
       <c r="O72">
-        <v>0.9510164900000001</v>
+        <v>0.948545297</v>
       </c>
       <c r="P72">
-        <v>2.219038476666667</v>
+        <v>2.213272359666667</v>
       </c>
       <c r="Q72">
-        <v>3.189038476666667</v>
+        <v>3.183272359666667</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3208275319496054</v>
+        <v>0.3292308175176859</v>
       </c>
       <c r="T72">
-        <v>1.917613667519734</v>
+        <v>1.976205093415143</v>
       </c>
       <c r="U72">
         <v>0.0543</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>6.497729176613424</v>
+        <v>6.406211864266756</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1224640370801289</v>
+        <v>0.1220728145753762</v>
       </c>
       <c r="C73">
-        <v>12.43465280055685</v>
+        <v>12.39992720741561</v>
       </c>
       <c r="D73">
-        <v>22.80535280055685</v>
+        <v>22.92232720741562</v>
       </c>
       <c r="E73">
-        <v>-3.029299999999999</v>
+        <v>-2.877599999999999</v>
       </c>
       <c r="F73">
-        <v>10.7707</v>
+        <v>10.9224</v>
       </c>
       <c r="G73">
         <v>0.4</v>
@@ -7261,28 +7261,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M73">
-        <v>0.5848490100000001</v>
+        <v>0.5930863200000001</v>
       </c>
       <c r="N73">
-        <v>3.161817656666667</v>
+        <v>3.153580346666667</v>
       </c>
       <c r="O73">
-        <v>0.948545297</v>
+        <v>0.946074104</v>
       </c>
       <c r="P73">
-        <v>2.213272359666667</v>
+        <v>2.207506242666667</v>
       </c>
       <c r="Q73">
-        <v>3.183272359666667</v>
+        <v>3.177506242666666</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3292308175176858</v>
+        <v>0.3382343377692006</v>
       </c>
       <c r="T73">
-        <v>1.976205093415142</v>
+        <v>2.038981621160223</v>
       </c>
       <c r="U73">
         <v>0.0543</v>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>6.406211864266756</v>
+        <v>6.317236699485273</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1220728145753762</v>
+        <v>0.1216815920706235</v>
       </c>
       <c r="C74">
-        <v>12.39992720741561</v>
+        <v>12.36640778349657</v>
       </c>
       <c r="D74">
-        <v>22.92232720741562</v>
+        <v>23.04050778349658</v>
       </c>
       <c r="E74">
-        <v>-2.877599999999999</v>
+        <v>-2.725899999999999</v>
       </c>
       <c r="F74">
-        <v>10.9224</v>
+        <v>11.0741</v>
       </c>
       <c r="G74">
         <v>0.4</v>
@@ -7343,28 +7343,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M74">
-        <v>0.5930863200000001</v>
+        <v>0.6013236300000001</v>
       </c>
       <c r="N74">
-        <v>3.153580346666667</v>
+        <v>3.145343036666667</v>
       </c>
       <c r="O74">
-        <v>0.946074104</v>
+        <v>0.943602911</v>
       </c>
       <c r="P74">
-        <v>2.207506242666667</v>
+        <v>2.201740125666667</v>
       </c>
       <c r="Q74">
-        <v>3.177506242666666</v>
+        <v>3.171740125666667</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3382343377692006</v>
+        <v>0.3479047854467535</v>
       </c>
       <c r="T74">
-        <v>2.038981621160223</v>
+        <v>2.106408262071606</v>
       </c>
       <c r="U74">
         <v>0.0543</v>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>6.317236699485273</v>
+        <v>6.230699210451228</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1216815920706235</v>
+        <v>0.1212903695658707</v>
       </c>
       <c r="C75">
-        <v>12.36640778349657</v>
+        <v>12.33411328141202</v>
       </c>
       <c r="D75">
-        <v>23.04050778349658</v>
+        <v>23.15991328141202</v>
       </c>
       <c r="E75">
-        <v>-2.725899999999999</v>
+        <v>-2.574199999999999</v>
       </c>
       <c r="F75">
-        <v>11.0741</v>
+        <v>11.2258</v>
       </c>
       <c r="G75">
         <v>0.4</v>
@@ -7425,28 +7425,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M75">
-        <v>0.6013236300000001</v>
+        <v>0.6095609400000001</v>
       </c>
       <c r="N75">
-        <v>3.145343036666667</v>
+        <v>3.137105726666667</v>
       </c>
       <c r="O75">
-        <v>0.943602911</v>
+        <v>0.9411317180000001</v>
       </c>
       <c r="P75">
-        <v>2.201740125666667</v>
+        <v>2.195974008666667</v>
       </c>
       <c r="Q75">
-        <v>3.171740125666667</v>
+        <v>3.165974008666667</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3479047854467535</v>
+        <v>0.3583191137148874</v>
       </c>
       <c r="T75">
-        <v>2.106408262071606</v>
+        <v>2.17902156766848</v>
       </c>
       <c r="U75">
         <v>0.0543</v>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>6.230699210451228</v>
+        <v>6.146500572472158</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1212903695658707</v>
+        <v>0.121424147061118</v>
       </c>
       <c r="C76">
-        <v>12.33411328141202</v>
+        <v>12.14144389121939</v>
       </c>
       <c r="D76">
-        <v>23.15991328141202</v>
+        <v>23.11894389121939</v>
       </c>
       <c r="E76">
-        <v>-2.574199999999999</v>
+        <v>-2.422499999999999</v>
       </c>
       <c r="F76">
-        <v>11.2258</v>
+        <v>11.3775</v>
       </c>
       <c r="G76">
         <v>0.4</v>
@@ -7507,45 +7507,45 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M76">
-        <v>0.6095609400000001</v>
+        <v>0.6291757500000001</v>
       </c>
       <c r="N76">
-        <v>3.137105726666667</v>
+        <v>3.117490916666667</v>
       </c>
       <c r="O76">
-        <v>0.9411317180000001</v>
+        <v>0.935247275</v>
       </c>
       <c r="P76">
-        <v>2.195974008666667</v>
+        <v>2.182243641666667</v>
       </c>
       <c r="Q76">
-        <v>3.165974008666667</v>
+        <v>3.152243641666667</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3583191137148874</v>
+        <v>0.3695665882444721</v>
       </c>
       <c r="T76">
-        <v>2.17902156766848</v>
+        <v>2.257443937713104</v>
       </c>
       <c r="U76">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V76">
         <v>0.3</v>
       </c>
       <c r="W76">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y76">
-        <v>6.146500572472158</v>
+        <v>5.954880916288758</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.121424147061118</v>
+        <v>0.1210399245563653</v>
       </c>
       <c r="C77">
-        <v>12.14144389121939</v>
+        <v>12.10780379866211</v>
       </c>
       <c r="D77">
-        <v>23.11894389121939</v>
+        <v>23.23700379866212</v>
       </c>
       <c r="E77">
-        <v>-2.422499999999999</v>
+        <v>-2.270799999999999</v>
       </c>
       <c r="F77">
-        <v>11.3775</v>
+        <v>11.5292</v>
       </c>
       <c r="G77">
         <v>0.4</v>
@@ -7589,28 +7589,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M77">
-        <v>0.6291757500000001</v>
+        <v>0.6375647600000001</v>
       </c>
       <c r="N77">
-        <v>3.117490916666667</v>
+        <v>3.109101906666667</v>
       </c>
       <c r="O77">
-        <v>0.935247275</v>
+        <v>0.9327305720000001</v>
       </c>
       <c r="P77">
-        <v>2.182243641666667</v>
+        <v>2.176371334666667</v>
       </c>
       <c r="Q77">
-        <v>3.152243641666667</v>
+        <v>3.146371334666667</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3695665882444721</v>
+        <v>0.3817513523181888</v>
       </c>
       <c r="T77">
-        <v>2.257443937713104</v>
+        <v>2.342401505261447</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>5.954880916288758</v>
+        <v>5.876527220021801</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1210399245563653</v>
+        <v>0.1206557020516126</v>
       </c>
       <c r="C78">
-        <v>12.10780379866211</v>
+        <v>12.07537567184973</v>
       </c>
       <c r="D78">
-        <v>23.23700379866212</v>
+        <v>23.35627567184974</v>
       </c>
       <c r="E78">
-        <v>-2.270799999999999</v>
+        <v>-2.1191</v>
       </c>
       <c r="F78">
-        <v>11.5292</v>
+        <v>11.6809</v>
       </c>
       <c r="G78">
         <v>0.4</v>
@@ -7671,28 +7671,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M78">
-        <v>0.6375647600000001</v>
+        <v>0.6459537700000001</v>
       </c>
       <c r="N78">
-        <v>3.109101906666667</v>
+        <v>3.100712896666667</v>
       </c>
       <c r="O78">
-        <v>0.9327305720000001</v>
+        <v>0.930213869</v>
       </c>
       <c r="P78">
-        <v>2.176371334666667</v>
+        <v>2.170499027666667</v>
       </c>
       <c r="Q78">
-        <v>3.146371334666667</v>
+        <v>3.140499027666666</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3817513523181888</v>
+        <v>0.3949956610939678</v>
       </c>
       <c r="T78">
-        <v>2.342401505261447</v>
+        <v>2.434746687379211</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>5.876527220021801</v>
+        <v>5.800208684696842</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1206557020516126</v>
+        <v>0.1202714795468599</v>
       </c>
       <c r="C79">
-        <v>12.07537567184973</v>
+        <v>12.04417826955475</v>
       </c>
       <c r="D79">
-        <v>23.35627567184974</v>
+        <v>23.47677826955475</v>
       </c>
       <c r="E79">
-        <v>-2.1191</v>
+        <v>-1.9674</v>
       </c>
       <c r="F79">
-        <v>11.6809</v>
+        <v>11.8326</v>
       </c>
       <c r="G79">
         <v>0.4</v>
@@ -7753,28 +7753,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M79">
-        <v>0.6459537700000001</v>
+        <v>0.6543427800000001</v>
       </c>
       <c r="N79">
-        <v>3.100712896666667</v>
+        <v>3.092323886666667</v>
       </c>
       <c r="O79">
-        <v>0.930213869</v>
+        <v>0.927697166</v>
       </c>
       <c r="P79">
-        <v>2.170499027666667</v>
+        <v>2.164626720666667</v>
       </c>
       <c r="Q79">
-        <v>3.140499027666666</v>
+        <v>3.134626720666667</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3949956610939678</v>
+        <v>0.4094439979402723</v>
       </c>
       <c r="T79">
-        <v>2.434746687379211</v>
+        <v>2.535486886053135</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>5.800208684696842</v>
+        <v>5.725847034893036</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1202714795468599</v>
+        <v>0.1198872570421072</v>
       </c>
       <c r="C80">
-        <v>12.04417826955475</v>
+        <v>12.01423073968772</v>
       </c>
       <c r="D80">
-        <v>23.47677826955475</v>
+        <v>23.59853073968772</v>
       </c>
       <c r="E80">
-        <v>-1.9674</v>
+        <v>-1.8157</v>
       </c>
       <c r="F80">
-        <v>11.8326</v>
+        <v>11.9843</v>
       </c>
       <c r="G80">
         <v>0.4</v>
@@ -7835,28 +7835,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M80">
-        <v>0.6543427800000001</v>
+        <v>0.66273179</v>
       </c>
       <c r="N80">
-        <v>3.092323886666667</v>
+        <v>3.083934876666667</v>
       </c>
       <c r="O80">
-        <v>0.927697166</v>
+        <v>0.925180463</v>
       </c>
       <c r="P80">
-        <v>2.164626720666667</v>
+        <v>2.158754413666667</v>
       </c>
       <c r="Q80">
-        <v>3.134626720666667</v>
+        <v>3.128754413666667</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4094439979402723</v>
+        <v>0.4252683668671771</v>
       </c>
       <c r="T80">
-        <v>2.535486886053135</v>
+        <v>2.645821389362671</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>5.725847034893036</v>
+        <v>5.653367958501986</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1198872570421072</v>
+        <v>0.1195030345373544</v>
       </c>
       <c r="C81">
-        <v>12.01423073968772</v>
+        <v>11.98555262944032</v>
       </c>
       <c r="D81">
-        <v>23.59853073968772</v>
+        <v>23.72155262944033</v>
       </c>
       <c r="E81">
-        <v>-1.8157</v>
+        <v>-1.663999999999998</v>
       </c>
       <c r="F81">
-        <v>11.9843</v>
+        <v>12.136</v>
       </c>
       <c r="G81">
         <v>0.4</v>
@@ -7917,28 +7917,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M81">
-        <v>0.66273179</v>
+        <v>0.6711208000000002</v>
       </c>
       <c r="N81">
-        <v>3.083934876666667</v>
+        <v>3.075545866666667</v>
       </c>
       <c r="O81">
-        <v>0.925180463</v>
+        <v>0.9226637600000001</v>
       </c>
       <c r="P81">
-        <v>2.158754413666667</v>
+        <v>2.152882106666667</v>
       </c>
       <c r="Q81">
-        <v>3.128754413666667</v>
+        <v>3.122882106666666</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4252683668671771</v>
+        <v>0.4426751726867724</v>
       </c>
       <c r="T81">
-        <v>2.645821389362671</v>
+        <v>2.76718934300316</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>5.653367958501986</v>
+        <v>5.58270085902071</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1195030345373544</v>
+        <v>0.1191188120326017</v>
       </c>
       <c r="C82">
-        <v>11.98555262944032</v>
+        <v>11.95816389574745</v>
       </c>
       <c r="D82">
-        <v>23.72155262944033</v>
+        <v>23.84586389574746</v>
       </c>
       <c r="E82">
-        <v>-1.663999999999998</v>
+        <v>-1.512299999999998</v>
       </c>
       <c r="F82">
-        <v>12.136</v>
+        <v>12.2877</v>
       </c>
       <c r="G82">
         <v>0.4</v>
@@ -7999,28 +7999,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M82">
-        <v>0.6711208000000002</v>
+        <v>0.6795098100000002</v>
       </c>
       <c r="N82">
-        <v>3.075545866666667</v>
+        <v>3.067156856666667</v>
       </c>
       <c r="O82">
-        <v>0.9226637600000001</v>
+        <v>0.920147057</v>
       </c>
       <c r="P82">
-        <v>2.152882106666667</v>
+        <v>2.147009799666667</v>
       </c>
       <c r="Q82">
-        <v>3.122882106666666</v>
+        <v>3.117009799666667</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4426751726867724</v>
+        <v>0.4619142738557988</v>
       </c>
       <c r="T82">
-        <v>2.76718934300316</v>
+        <v>2.90133287071107</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>5.58270085902071</v>
+        <v>5.513778626193293</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1191188120326017</v>
+        <v>0.118734589527849</v>
       </c>
       <c r="C83">
-        <v>11.95816389574745</v>
+        <v>11.9320849160799</v>
       </c>
       <c r="D83">
-        <v>23.84586389574746</v>
+        <v>23.9714849160799</v>
       </c>
       <c r="E83">
-        <v>-1.512299999999998</v>
+        <v>-1.360599999999998</v>
       </c>
       <c r="F83">
-        <v>12.2877</v>
+        <v>12.4394</v>
       </c>
       <c r="G83">
         <v>0.4</v>
@@ -8081,28 +8081,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M83">
-        <v>0.6795098100000002</v>
+        <v>0.6878988200000001</v>
       </c>
       <c r="N83">
-        <v>3.067156856666667</v>
+        <v>3.058767846666667</v>
       </c>
       <c r="O83">
-        <v>0.920147057</v>
+        <v>0.917630354</v>
       </c>
       <c r="P83">
-        <v>2.147009799666667</v>
+        <v>2.141137492666667</v>
       </c>
       <c r="Q83">
-        <v>3.117009799666667</v>
+        <v>3.111137492666667</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4619142738557988</v>
+        <v>0.4832910529324947</v>
       </c>
       <c r="T83">
-        <v>2.90133287071107</v>
+        <v>3.05038123483097</v>
       </c>
       <c r="U83">
         <v>0.0553</v>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>5.513778626193293</v>
+        <v>5.446537423434839</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.118734589527849</v>
+        <v>0.1183503670230963</v>
       </c>
       <c r="C84">
-        <v>11.9320849160799</v>
+        <v>11.90733649958003</v>
       </c>
       <c r="D84">
-        <v>23.9714849160799</v>
+        <v>24.09843649958003</v>
       </c>
       <c r="E84">
-        <v>-1.360599999999998</v>
+        <v>-1.208899999999998</v>
       </c>
       <c r="F84">
-        <v>12.4394</v>
+        <v>12.5911</v>
       </c>
       <c r="G84">
         <v>0.4</v>
@@ -8163,28 +8163,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M84">
-        <v>0.6878988200000001</v>
+        <v>0.6962878300000002</v>
       </c>
       <c r="N84">
-        <v>3.058767846666667</v>
+        <v>3.050378836666667</v>
       </c>
       <c r="O84">
-        <v>0.917630354</v>
+        <v>0.915113651</v>
       </c>
       <c r="P84">
-        <v>2.141137492666667</v>
+        <v>2.135265185666667</v>
       </c>
       <c r="Q84">
-        <v>3.111137492666667</v>
+        <v>3.105265185666667</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4832910529324947</v>
+        <v>0.5071827471946844</v>
       </c>
       <c r="T84">
-        <v>3.05038123483097</v>
+        <v>3.216964700612034</v>
       </c>
       <c r="U84">
         <v>0.0553</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>5.446537423434839</v>
+        <v>5.380916490622371</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1183503670230963</v>
+        <v>0.1179661445183436</v>
       </c>
       <c r="C85">
-        <v>11.90733649958003</v>
+        <v>11.8839398985532</v>
       </c>
       <c r="D85">
-        <v>24.09843649958003</v>
+        <v>24.22673989855321</v>
       </c>
       <c r="E85">
-        <v>-1.208899999999998</v>
+        <v>-1.057199999999998</v>
       </c>
       <c r="F85">
-        <v>12.5911</v>
+        <v>12.7428</v>
       </c>
       <c r="G85">
         <v>0.4</v>
@@ -8245,28 +8245,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M85">
-        <v>0.6962878300000002</v>
+        <v>0.7046768400000002</v>
       </c>
       <c r="N85">
-        <v>3.050378836666667</v>
+        <v>3.041989826666667</v>
       </c>
       <c r="O85">
-        <v>0.915113651</v>
+        <v>0.912596948</v>
       </c>
       <c r="P85">
-        <v>2.135265185666667</v>
+        <v>2.129392878666667</v>
       </c>
       <c r="Q85">
-        <v>3.105265185666667</v>
+        <v>3.099392878666666</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5071827471946844</v>
+        <v>0.5340609032396477</v>
       </c>
       <c r="T85">
-        <v>3.216964700612034</v>
+        <v>3.404371099615731</v>
       </c>
       <c r="U85">
         <v>0.0553</v>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>5.380916490622371</v>
+        <v>5.316857960972104</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1179661445183436</v>
+        <v>0.1175819220135909</v>
       </c>
       <c r="C86">
-        <v>11.88393989855321</v>
+        <v>11.8619168203282</v>
       </c>
       <c r="D86">
-        <v>24.22673989855321</v>
+        <v>24.3564168203282</v>
       </c>
       <c r="E86">
-        <v>-1.0572</v>
+        <v>-0.9055</v>
       </c>
       <c r="F86">
-        <v>12.7428</v>
+        <v>12.8945</v>
       </c>
       <c r="G86">
         <v>0.4</v>
@@ -8327,28 +8327,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M86">
-        <v>0.7046768400000001</v>
+        <v>0.7130658500000001</v>
       </c>
       <c r="N86">
-        <v>3.041989826666667</v>
+        <v>3.033600816666667</v>
       </c>
       <c r="O86">
-        <v>0.912596948</v>
+        <v>0.9100802450000001</v>
       </c>
       <c r="P86">
-        <v>2.129392878666667</v>
+        <v>2.123520571666667</v>
       </c>
       <c r="Q86">
-        <v>3.099392878666666</v>
+        <v>3.093520571666667</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5340609032396474</v>
+        <v>0.5645228134239391</v>
       </c>
       <c r="T86">
-        <v>3.404371099615729</v>
+        <v>3.616765018486586</v>
       </c>
       <c r="U86">
         <v>0.0553</v>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>5.316857960972105</v>
+        <v>5.254306690843022</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1175819220135909</v>
+        <v>0.1171976995088382</v>
       </c>
       <c r="C87">
-        <v>11.8619168203282</v>
+        <v>11.8412894395006</v>
       </c>
       <c r="D87">
-        <v>24.3564168203282</v>
+        <v>24.48748943950061</v>
       </c>
       <c r="E87">
-        <v>-0.9055</v>
+        <v>-0.7538</v>
       </c>
       <c r="F87">
-        <v>12.8945</v>
+        <v>13.0462</v>
       </c>
       <c r="G87">
         <v>0.4</v>
@@ -8409,28 +8409,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M87">
-        <v>0.7130658500000001</v>
+        <v>0.72145486</v>
       </c>
       <c r="N87">
-        <v>3.033600816666667</v>
+        <v>3.025211806666667</v>
       </c>
       <c r="O87">
-        <v>0.9100802450000001</v>
+        <v>0.907563542</v>
       </c>
       <c r="P87">
-        <v>2.123520571666667</v>
+        <v>2.117648264666667</v>
       </c>
       <c r="Q87">
-        <v>3.093520571666667</v>
+        <v>3.087648264666667</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5645228134239391</v>
+        <v>0.5993364250631296</v>
       </c>
       <c r="T87">
-        <v>3.616765018486586</v>
+        <v>3.859500925767564</v>
       </c>
       <c r="U87">
         <v>0.0553</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>5.254306690843022</v>
+        <v>5.193210101414615</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1171976995088382</v>
+        <v>0.1168134770040854</v>
       </c>
       <c r="C88">
-        <v>11.8412894395006</v>
+        <v>11.82208041057374</v>
       </c>
       <c r="D88">
-        <v>24.48748943950061</v>
+        <v>24.61998041057374</v>
       </c>
       <c r="E88">
-        <v>-0.7538</v>
+        <v>-0.6021000000000001</v>
       </c>
       <c r="F88">
-        <v>13.0462</v>
+        <v>13.1979</v>
       </c>
       <c r="G88">
         <v>0.4</v>
@@ -8491,28 +8491,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M88">
-        <v>0.72145486</v>
+        <v>0.7298438700000001</v>
       </c>
       <c r="N88">
-        <v>3.025211806666667</v>
+        <v>3.016822796666667</v>
       </c>
       <c r="O88">
-        <v>0.907563542</v>
+        <v>0.9050468390000002</v>
       </c>
       <c r="P88">
-        <v>2.117648264666667</v>
+        <v>2.111775957666667</v>
       </c>
       <c r="Q88">
-        <v>3.087648264666667</v>
+        <v>3.081775957666667</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5993364250631296</v>
+        <v>0.6395059769545033</v>
       </c>
       <c r="T88">
-        <v>3.859500925767564</v>
+        <v>4.139580818784078</v>
       </c>
       <c r="U88">
         <v>0.0553</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>5.193210101414615</v>
+        <v>5.133518031283413</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1168134770040854</v>
+        <v>0.1164292544993328</v>
       </c>
       <c r="C89">
-        <v>11.82208041057374</v>
+        <v>11.80431288101206</v>
       </c>
       <c r="D89">
-        <v>24.61998041057374</v>
+        <v>24.75391288101206</v>
       </c>
       <c r="E89">
-        <v>-0.6021000000000001</v>
+        <v>-0.4503999999999984</v>
       </c>
       <c r="F89">
-        <v>13.1979</v>
+        <v>13.3496</v>
       </c>
       <c r="G89">
         <v>0.4</v>
@@ -8573,28 +8573,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M89">
-        <v>0.7298438700000001</v>
+        <v>0.7382328800000002</v>
       </c>
       <c r="N89">
-        <v>3.016822796666667</v>
+        <v>3.008433786666667</v>
       </c>
       <c r="O89">
-        <v>0.9050468390000002</v>
+        <v>0.9025301360000001</v>
       </c>
       <c r="P89">
-        <v>2.111775957666667</v>
+        <v>2.105903650666667</v>
       </c>
       <c r="Q89">
-        <v>3.081775957666667</v>
+        <v>3.075903650666667</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6395059769545033</v>
+        <v>0.6863704541611062</v>
       </c>
       <c r="T89">
-        <v>4.139580818784078</v>
+        <v>4.466340693970013</v>
       </c>
       <c r="U89">
         <v>0.0553</v>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>5.133518031283413</v>
+        <v>5.075182599109737</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1164292544993328</v>
+        <v>0.11604503199458</v>
       </c>
       <c r="C90">
-        <v>11.80431288101206</v>
+        <v>11.78801050472311</v>
       </c>
       <c r="D90">
-        <v>24.75391288101206</v>
+        <v>24.88931050472312</v>
       </c>
       <c r="E90">
-        <v>-0.4503999999999984</v>
+        <v>-0.2986999999999984</v>
       </c>
       <c r="F90">
-        <v>13.3496</v>
+        <v>13.5013</v>
       </c>
       <c r="G90">
         <v>0.4</v>
@@ -8655,28 +8655,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M90">
-        <v>0.7382328800000002</v>
+        <v>0.7466218900000001</v>
       </c>
       <c r="N90">
-        <v>3.008433786666667</v>
+        <v>3.000044776666667</v>
       </c>
       <c r="O90">
-        <v>0.9025301360000001</v>
+        <v>0.900013433</v>
       </c>
       <c r="P90">
-        <v>2.105903650666667</v>
+        <v>2.100031343666667</v>
       </c>
       <c r="Q90">
-        <v>3.075903650666667</v>
+        <v>3.070031343666667</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6863704541611062</v>
+        <v>0.741755745405273</v>
       </c>
       <c r="T90">
-        <v>4.466340693970013</v>
+        <v>4.852511455553389</v>
       </c>
       <c r="U90">
         <v>0.0553</v>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>5.075182599109737</v>
+        <v>5.018158075524235</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.11604503199458</v>
+        <v>0.1156608094898273</v>
       </c>
       <c r="C91">
-        <v>11.78801050472311</v>
+        <v>11.77319745598419</v>
       </c>
       <c r="D91">
-        <v>24.88931050472312</v>
+        <v>25.02619745598419</v>
       </c>
       <c r="E91">
-        <v>-0.2986999999999984</v>
+        <v>-0.1469999999999985</v>
       </c>
       <c r="F91">
-        <v>13.5013</v>
+        <v>13.653</v>
       </c>
       <c r="G91">
         <v>0.4</v>
@@ -8737,28 +8737,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M91">
-        <v>0.7466218900000001</v>
+        <v>0.7550109000000002</v>
       </c>
       <c r="N91">
-        <v>3.000044776666667</v>
+        <v>2.991655766666667</v>
       </c>
       <c r="O91">
-        <v>0.900013433</v>
+        <v>0.89749673</v>
       </c>
       <c r="P91">
-        <v>2.100031343666667</v>
+        <v>2.094159036666667</v>
       </c>
       <c r="Q91">
-        <v>3.070031343666667</v>
+        <v>3.064159036666667</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.741755745405273</v>
+        <v>0.8082180948982731</v>
       </c>
       <c r="T91">
-        <v>4.852511455553389</v>
+        <v>5.315916369453439</v>
       </c>
       <c r="U91">
         <v>0.0553</v>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>5.018158075524235</v>
+        <v>4.962400763573965</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1156608094898273</v>
+        <v>0.1152765869850746</v>
       </c>
       <c r="C92">
-        <v>11.77319745598419</v>
+        <v>11.75989844383122</v>
       </c>
       <c r="D92">
-        <v>25.02619745598419</v>
+        <v>25.16459844383122</v>
       </c>
       <c r="E92">
-        <v>-0.1469999999999985</v>
+        <v>0.004700000000001481</v>
       </c>
       <c r="F92">
-        <v>13.653</v>
+        <v>13.8047</v>
       </c>
       <c r="G92">
         <v>0.4</v>
@@ -8819,28 +8819,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M92">
-        <v>0.7550109000000002</v>
+        <v>0.7633999100000002</v>
       </c>
       <c r="N92">
-        <v>2.991655766666667</v>
+        <v>2.983266756666667</v>
       </c>
       <c r="O92">
-        <v>0.89749673</v>
+        <v>0.894980027</v>
       </c>
       <c r="P92">
-        <v>2.094159036666667</v>
+        <v>2.088286729666667</v>
       </c>
       <c r="Q92">
-        <v>3.064159036666667</v>
+        <v>3.058286729666666</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.8082180948982731</v>
+        <v>0.8894498553897178</v>
       </c>
       <c r="T92">
-        <v>5.315916369453439</v>
+        <v>5.882300153109057</v>
       </c>
       <c r="U92">
         <v>0.0553</v>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>4.962400763573965</v>
+        <v>4.907868887051174</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1152765869850746</v>
+        <v>0.1148923644803219</v>
       </c>
       <c r="C93">
-        <v>11.75989844383122</v>
+        <v>11.74813872692773</v>
       </c>
       <c r="D93">
-        <v>25.16459844383122</v>
+        <v>25.30453872692774</v>
       </c>
       <c r="E93">
-        <v>0.004700000000001481</v>
+        <v>0.1564000000000014</v>
       </c>
       <c r="F93">
-        <v>13.8047</v>
+        <v>13.9564</v>
       </c>
       <c r="G93">
         <v>0.4</v>
@@ -8901,28 +8901,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M93">
-        <v>0.7633999100000002</v>
+        <v>0.7717889200000001</v>
       </c>
       <c r="N93">
-        <v>2.983266756666667</v>
+        <v>2.974877746666667</v>
       </c>
       <c r="O93">
-        <v>0.894980027</v>
+        <v>0.8924633240000001</v>
       </c>
       <c r="P93">
-        <v>2.088286729666667</v>
+        <v>2.082414422666667</v>
       </c>
       <c r="Q93">
-        <v>3.058286729666666</v>
+        <v>3.052414422666667</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.8894498553897178</v>
+        <v>0.9909895560040239</v>
       </c>
       <c r="T93">
-        <v>5.882300153109057</v>
+        <v>6.590279882678582</v>
       </c>
       <c r="U93">
         <v>0.0553</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>4.907868887051174</v>
+        <v>4.854522486104965</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1148923644803219</v>
+        <v>0.1145081419755692</v>
       </c>
       <c r="C94">
-        <v>11.74813872692773</v>
+        <v>11.73794412893278</v>
       </c>
       <c r="D94">
-        <v>25.30453872692774</v>
+        <v>25.44604412893279</v>
       </c>
       <c r="E94">
-        <v>0.1564000000000014</v>
+        <v>0.3081000000000014</v>
       </c>
       <c r="F94">
-        <v>13.9564</v>
+        <v>14.1081</v>
       </c>
       <c r="G94">
         <v>0.4</v>
@@ -8983,28 +8983,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M94">
-        <v>0.7717889200000001</v>
+        <v>0.7801779300000001</v>
       </c>
       <c r="N94">
-        <v>2.974877746666667</v>
+        <v>2.966488736666667</v>
       </c>
       <c r="O94">
-        <v>0.8924633240000001</v>
+        <v>0.889946621</v>
       </c>
       <c r="P94">
-        <v>2.082414422666667</v>
+        <v>2.076542115666667</v>
       </c>
       <c r="Q94">
-        <v>3.052414422666667</v>
+        <v>3.046542115666667</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.9909895560040239</v>
+        <v>1.121540599650989</v>
       </c>
       <c r="T94">
-        <v>6.590279882678582</v>
+        <v>7.500539534982254</v>
       </c>
       <c r="U94">
         <v>0.0553</v>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>4.854522486104965</v>
+        <v>4.802323319587708</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1145081419755692</v>
+        <v>0.1141239194708165</v>
       </c>
       <c r="C95">
-        <v>11.73794412893278</v>
+        <v>11.72934105438716</v>
       </c>
       <c r="D95">
-        <v>25.44604412893279</v>
+        <v>25.58914105438716</v>
       </c>
       <c r="E95">
-        <v>0.3081000000000014</v>
+        <v>0.4598000000000013</v>
       </c>
       <c r="F95">
-        <v>14.1081</v>
+        <v>14.2598</v>
       </c>
       <c r="G95">
         <v>0.4</v>
@@ -9065,28 +9065,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M95">
-        <v>0.7801779300000001</v>
+        <v>0.7885669400000002</v>
       </c>
       <c r="N95">
-        <v>2.966488736666667</v>
+        <v>2.958099726666667</v>
       </c>
       <c r="O95">
-        <v>0.889946621</v>
+        <v>0.8874299180000002</v>
       </c>
       <c r="P95">
-        <v>2.076542115666667</v>
+        <v>2.070669808666667</v>
       </c>
       <c r="Q95">
-        <v>3.046542115666667</v>
+        <v>3.040669808666667</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.121540599650989</v>
+        <v>1.295608657846942</v>
       </c>
       <c r="T95">
-        <v>7.500539534982254</v>
+        <v>8.714219071387152</v>
       </c>
       <c r="U95">
         <v>0.0553</v>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>4.802323319587708</v>
+        <v>4.751234773634647</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1141239194708165</v>
+        <v>0.1137396969660637</v>
       </c>
       <c r="C96">
-        <v>11.72934105438716</v>
+        <v>11.722356505139</v>
       </c>
       <c r="D96">
-        <v>25.58914105438716</v>
+        <v>25.73385650513901</v>
       </c>
       <c r="E96">
-        <v>0.4598000000000013</v>
+        <v>0.6115000000000013</v>
       </c>
       <c r="F96">
-        <v>14.2598</v>
+        <v>14.4115</v>
       </c>
       <c r="G96">
         <v>0.4</v>
@@ -9147,28 +9147,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M96">
-        <v>0.7885669400000002</v>
+        <v>0.7969559500000002</v>
       </c>
       <c r="N96">
-        <v>2.958099726666667</v>
+        <v>2.949710716666667</v>
       </c>
       <c r="O96">
-        <v>0.8874299180000002</v>
+        <v>0.8849132150000001</v>
       </c>
       <c r="P96">
-        <v>2.070669808666667</v>
+        <v>2.064797501666667</v>
       </c>
       <c r="Q96">
-        <v>3.040669808666667</v>
+        <v>3.034797501666667</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.295608657846942</v>
+        <v>1.539303939321277</v>
       </c>
       <c r="T96">
-        <v>8.714219071387152</v>
+        <v>10.41337042235401</v>
       </c>
       <c r="U96">
         <v>0.0553</v>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>4.751234773634647</v>
+        <v>4.70122177601744</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1137396969660637</v>
+        <v>0.113355474461311</v>
       </c>
       <c r="C97">
-        <v>11.722356505139</v>
+        <v>11.71701809732964</v>
       </c>
       <c r="D97">
-        <v>25.73385650513901</v>
+        <v>25.88021809732964</v>
       </c>
       <c r="E97">
-        <v>0.6115000000000013</v>
+        <v>0.7632000000000012</v>
       </c>
       <c r="F97">
-        <v>14.4115</v>
+        <v>14.5632</v>
       </c>
       <c r="G97">
         <v>0.4</v>
@@ -9229,28 +9229,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M97">
-        <v>0.7969559500000002</v>
+        <v>0.8053449600000001</v>
       </c>
       <c r="N97">
-        <v>2.949710716666667</v>
+        <v>2.941321706666667</v>
       </c>
       <c r="O97">
-        <v>0.8849132150000001</v>
+        <v>0.882396512</v>
       </c>
       <c r="P97">
-        <v>2.064797501666667</v>
+        <v>2.058925194666667</v>
       </c>
       <c r="Q97">
-        <v>3.034797501666667</v>
+        <v>3.028925194666667</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.539303939321277</v>
+        <v>1.904846861532779</v>
       </c>
       <c r="T97">
-        <v>10.41337042235401</v>
+        <v>12.9620974488043</v>
       </c>
       <c r="U97">
         <v>0.0553</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>4.70122177601744</v>
+        <v>4.652250715850592</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.113355474461311</v>
+        <v>0.1129712519565583</v>
       </c>
       <c r="C98">
-        <v>11.71701809732964</v>
+        <v>11.71335407896258</v>
       </c>
       <c r="D98">
-        <v>25.88021809732964</v>
+        <v>26.02825407896258</v>
       </c>
       <c r="E98">
-        <v>0.7632000000000012</v>
+        <v>0.9149000000000012</v>
       </c>
       <c r="F98">
-        <v>14.5632</v>
+        <v>14.7149</v>
       </c>
       <c r="G98">
         <v>0.4</v>
@@ -9311,28 +9311,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M98">
-        <v>0.8053449600000001</v>
+        <v>0.8137339700000001</v>
       </c>
       <c r="N98">
-        <v>2.941321706666667</v>
+        <v>2.932932696666667</v>
       </c>
       <c r="O98">
-        <v>0.882396512</v>
+        <v>0.879879809</v>
       </c>
       <c r="P98">
-        <v>2.058925194666667</v>
+        <v>2.053052887666666</v>
       </c>
       <c r="Q98">
-        <v>3.028925194666667</v>
+        <v>3.023052887666666</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.904846861532774</v>
+        <v>2.514085065218608</v>
       </c>
       <c r="T98">
-        <v>12.96209744880426</v>
+        <v>17.20997582622139</v>
       </c>
       <c r="U98">
         <v>0.0553</v>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>4.652250715850592</v>
+        <v>4.604289368264503</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1129712519565583</v>
+        <v>0.1125870294518056</v>
       </c>
       <c r="C99">
-        <v>11.71335407896258</v>
+        <v>11.71139334807884</v>
       </c>
       <c r="D99">
-        <v>26.02825407896258</v>
+        <v>26.17799334807884</v>
       </c>
       <c r="E99">
-        <v>0.9149000000000012</v>
+        <v>1.066600000000001</v>
       </c>
       <c r="F99">
-        <v>14.7149</v>
+        <v>14.8666</v>
       </c>
       <c r="G99">
         <v>0.4</v>
@@ -9393,28 +9393,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M99">
-        <v>0.8137339700000001</v>
+        <v>0.8221229800000002</v>
       </c>
       <c r="N99">
-        <v>2.932932696666667</v>
+        <v>2.924543686666667</v>
       </c>
       <c r="O99">
-        <v>0.879879809</v>
+        <v>0.8773631060000001</v>
       </c>
       <c r="P99">
-        <v>2.053052887666666</v>
+        <v>2.047180580666667</v>
       </c>
       <c r="Q99">
-        <v>3.023052887666666</v>
+        <v>3.017180580666667</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.514085065218608</v>
+        <v>3.732561472590276</v>
       </c>
       <c r="T99">
-        <v>17.20997582622139</v>
+        <v>25.70573258105565</v>
       </c>
       <c r="U99">
         <v>0.0553</v>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>4.604289368264503</v>
+        <v>4.557306823690376</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1125870294518056</v>
+        <v>0.1122028069470529</v>
       </c>
       <c r="C100">
-        <v>11.71139334807884</v>
+        <v>11.71116547156329</v>
       </c>
       <c r="D100">
-        <v>26.17799334807884</v>
+        <v>26.3294654715633</v>
       </c>
       <c r="E100">
-        <v>1.066600000000001</v>
+        <v>1.218300000000001</v>
       </c>
       <c r="F100">
-        <v>14.8666</v>
+        <v>15.0183</v>
       </c>
       <c r="G100">
         <v>0.4</v>
@@ -9475,28 +9475,28 @@
         <v>3.746666666666667</v>
       </c>
       <c r="M100">
-        <v>0.8221229800000002</v>
+        <v>0.8305119900000001</v>
       </c>
       <c r="N100">
-        <v>2.924543686666667</v>
+        <v>2.916154676666667</v>
       </c>
       <c r="O100">
-        <v>0.8773631060000001</v>
+        <v>0.8748464030000001</v>
       </c>
       <c r="P100">
-        <v>2.047180580666667</v>
+        <v>2.041308273666667</v>
       </c>
       <c r="Q100">
-        <v>3.017180580666667</v>
+        <v>3.011308273666667</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.732561472590276</v>
+        <v>7.38799069470528</v>
       </c>
       <c r="T100">
-        <v>25.70573258105565</v>
+        <v>51.19300284555841</v>
       </c>
       <c r="U100">
         <v>0.0553</v>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>4.557306823690376</v>
+        <v>4.511273421430877</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1122028069470529</v>
-      </c>
-      <c r="C101">
-        <v>11.71116547156329</v>
-      </c>
-      <c r="D101">
-        <v>26.3294654715633</v>
-      </c>
-      <c r="E101">
-        <v>1.218300000000001</v>
-      </c>
-      <c r="F101">
-        <v>15.0183</v>
-      </c>
-      <c r="G101">
-        <v>0.4</v>
-      </c>
-      <c r="H101">
-        <v>1.37</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>4.716666666666667</v>
-      </c>
-      <c r="K101">
-        <v>0.97</v>
-      </c>
-      <c r="L101">
-        <v>3.746666666666667</v>
-      </c>
-      <c r="M101">
-        <v>0.8305119900000001</v>
-      </c>
-      <c r="N101">
-        <v>2.916154676666667</v>
-      </c>
-      <c r="O101">
-        <v>0.8748464030000001</v>
-      </c>
-      <c r="P101">
-        <v>2.041308273666667</v>
-      </c>
-      <c r="Q101">
-        <v>3.011308273666667</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>7.38799069470528</v>
-      </c>
-      <c r="T101">
-        <v>51.19300284555841</v>
-      </c>
-      <c r="U101">
-        <v>0.0553</v>
-      </c>
-      <c r="V101">
-        <v>0.3</v>
-      </c>
-      <c r="W101">
-        <v>0.03871</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A3/A-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>4.511273421430877</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
